--- a/data/Logon.xlsx
+++ b/data/Logon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\Infos PG armazem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEBA718C-D15F-4FB6-8348-14399904A569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A842880B-4149-4C4B-BE6D-F66CF5BBF4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{74901FF2-A7B0-4E61-9002-F08ADAC3CD93}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{74901FF2-A7B0-4E61-9002-F08ADAC3CD93}"/>
   </bookViews>
   <sheets>
     <sheet name="Logon" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="280">
   <si>
     <t>NOME</t>
   </si>
@@ -798,6 +798,84 @@
   </si>
   <si>
     <t>LEANDRO APARECIDO FELISBERTO</t>
+  </si>
+  <si>
+    <t>ARNALDO IE</t>
+  </si>
+  <si>
+    <t>MARCIO APA</t>
+  </si>
+  <si>
+    <t>YAGO GUILH</t>
+  </si>
+  <si>
+    <t>WILIAM JAR</t>
+  </si>
+  <si>
+    <t>RONI CRIST</t>
+  </si>
+  <si>
+    <t>TATIANE VI</t>
+  </si>
+  <si>
+    <t>CLAYTON AN</t>
+  </si>
+  <si>
+    <t>BRUNO DA S</t>
+  </si>
+  <si>
+    <t>DHAYMON DO</t>
+  </si>
+  <si>
+    <t>RAFAEL WIL</t>
+  </si>
+  <si>
+    <t>JUCI VICEN</t>
+  </si>
+  <si>
+    <t>SUIANI VAZ</t>
+  </si>
+  <si>
+    <t>ELIRIANE D</t>
+  </si>
+  <si>
+    <t>ARNALDO IENK</t>
+  </si>
+  <si>
+    <t>MARCIO APARECIDO DA VEIGA</t>
+  </si>
+  <si>
+    <t>YAGO GUILHERME PEREIRA DA CUNHA</t>
+  </si>
+  <si>
+    <t>WILIAM JARDEL DE MELO</t>
+  </si>
+  <si>
+    <t>RONI CRISTIAN COSTA ROSA</t>
+  </si>
+  <si>
+    <t>TATIANE VIRGINIA PETROCHINSKI</t>
+  </si>
+  <si>
+    <t>CLAYTON ANANIAS PEREIRA</t>
+  </si>
+  <si>
+    <t>BRUNO DA SILVA ALMEIDA</t>
+  </si>
+  <si>
+    <t>DHAYMON DOMINGOS E SILVA</t>
+  </si>
+  <si>
+    <t>RAFAEL WILLIAN DE ANDRADE</t>
+  </si>
+  <si>
+    <t>JUCI VICENTE BARBOZA</t>
+  </si>
+  <si>
+    <t>SUIANI VAZ DA CUNHA</t>
+  </si>
+  <si>
+    <t>ELIRIANE DE FREITAS</t>
   </si>
 </sst>
 </file>
@@ -1167,15 +1245,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{135F57B4-099B-4A96-981A-838F40082E5A}">
-  <dimension ref="A1:P233"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P350"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="2"/>
-    <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" style="2"/>
+    <col min="16" max="16" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1225,7 +1303,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>132</v>
       </c>
@@ -1275,7 +1353,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>134</v>
       </c>
@@ -1325,7 +1403,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>135</v>
       </c>
@@ -1375,7 +1453,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>136</v>
       </c>
@@ -1425,7 +1503,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -1475,7 +1553,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -1525,7 +1603,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>139</v>
       </c>
@@ -1575,7 +1653,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -1625,7 +1703,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>141</v>
       </c>
@@ -1675,7 +1753,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>142</v>
       </c>
@@ -1725,7 +1803,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>143</v>
       </c>
@@ -1775,7 +1853,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>144</v>
       </c>
@@ -1825,7 +1903,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>145</v>
       </c>
@@ -1875,7 +1953,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>146</v>
       </c>
@@ -1925,7 +2003,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>147</v>
       </c>
@@ -1975,7 +2053,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>148</v>
       </c>
@@ -2025,7 +2103,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>149</v>
       </c>
@@ -2075,7 +2153,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>150</v>
       </c>
@@ -2125,7 +2203,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -2175,7 +2253,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>152</v>
       </c>
@@ -2225,7 +2303,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>153</v>
       </c>
@@ -2275,7 +2353,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>154</v>
       </c>
@@ -2325,7 +2403,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>155</v>
       </c>
@@ -2375,7 +2453,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>156</v>
       </c>
@@ -2425,7 +2503,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>157</v>
       </c>
@@ -2475,7 +2553,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>158</v>
       </c>
@@ -2525,7 +2603,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>159</v>
       </c>
@@ -2575,7 +2653,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>160</v>
       </c>
@@ -2625,7 +2703,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>161</v>
       </c>
@@ -2675,7 +2753,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>162</v>
       </c>
@@ -2725,7 +2803,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>163</v>
       </c>
@@ -2775,7 +2853,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>164</v>
       </c>
@@ -2825,7 +2903,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>165</v>
       </c>
@@ -2875,7 +2953,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -2925,7 +3003,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>167</v>
       </c>
@@ -2975,7 +3053,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>168</v>
       </c>
@@ -3025,7 +3103,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>169</v>
       </c>
@@ -3075,7 +3153,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>170</v>
       </c>
@@ -3125,7 +3203,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>171</v>
       </c>
@@ -3175,7 +3253,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>172</v>
       </c>
@@ -3225,7 +3303,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>173</v>
       </c>
@@ -3275,7 +3353,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>174</v>
       </c>
@@ -3325,7 +3403,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>175</v>
       </c>
@@ -3375,7 +3453,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>176</v>
       </c>
@@ -3425,7 +3503,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>177</v>
       </c>
@@ -3475,7 +3553,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>178</v>
       </c>
@@ -3525,7 +3603,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>179</v>
       </c>
@@ -3575,7 +3653,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>180</v>
       </c>
@@ -3625,7 +3703,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>181</v>
       </c>
@@ -3675,7 +3753,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>182</v>
       </c>
@@ -3725,7 +3803,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>183</v>
       </c>
@@ -3775,7 +3853,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>184</v>
       </c>
@@ -3825,7 +3903,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>185</v>
       </c>
@@ -3875,7 +3953,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>186</v>
       </c>
@@ -3925,7 +4003,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>187</v>
       </c>
@@ -3975,7 +4053,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>188</v>
       </c>
@@ -4025,7 +4103,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>189</v>
       </c>
@@ -4075,7 +4153,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>190</v>
       </c>
@@ -4125,7 +4203,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>191</v>
       </c>
@@ -4175,7 +4253,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>192</v>
       </c>
@@ -4225,7 +4303,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>193</v>
       </c>
@@ -4275,7 +4353,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>194</v>
       </c>
@@ -4325,7 +4403,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>195</v>
       </c>
@@ -4375,7 +4453,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>196</v>
       </c>
@@ -4425,7 +4503,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>197</v>
       </c>
@@ -4475,7 +4553,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>198</v>
       </c>
@@ -4525,7 +4603,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>199</v>
       </c>
@@ -4575,7 +4653,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>200</v>
       </c>
@@ -4625,7 +4703,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>201</v>
       </c>
@@ -4675,7 +4753,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>202</v>
       </c>
@@ -4725,7 +4803,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>203</v>
       </c>
@@ -4775,7 +4853,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>204</v>
       </c>
@@ -4825,7 +4903,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>205</v>
       </c>
@@ -4875,7 +4953,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>206</v>
       </c>
@@ -4925,7 +5003,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>207</v>
       </c>
@@ -4975,7 +5053,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>208</v>
       </c>
@@ -5025,7 +5103,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>209</v>
       </c>
@@ -5075,7 +5153,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>210</v>
       </c>
@@ -5125,7 +5203,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>211</v>
       </c>
@@ -5175,7 +5253,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>212</v>
       </c>
@@ -5225,7 +5303,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>213</v>
       </c>
@@ -5275,7 +5353,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>214</v>
       </c>
@@ -5325,7 +5403,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>215</v>
       </c>
@@ -5375,7 +5453,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>216</v>
       </c>
@@ -5425,7 +5503,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>217</v>
       </c>
@@ -5475,7 +5553,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>218</v>
       </c>
@@ -5525,7 +5603,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>219</v>
       </c>
@@ -5575,7 +5653,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>220</v>
       </c>
@@ -5625,7 +5703,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>221</v>
       </c>
@@ -5675,7 +5753,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>222</v>
       </c>
@@ -5725,7 +5803,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>223</v>
       </c>
@@ -5775,7 +5853,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>224</v>
       </c>
@@ -5825,7 +5903,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>225</v>
       </c>
@@ -5875,7 +5953,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>226</v>
       </c>
@@ -5925,7 +6003,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>227</v>
       </c>
@@ -5975,7 +6053,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>228</v>
       </c>
@@ -6025,7 +6103,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>229</v>
       </c>
@@ -6075,7 +6153,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>230</v>
       </c>
@@ -6125,7 +6203,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>231</v>
       </c>
@@ -6175,7 +6253,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>232</v>
       </c>
@@ -6225,7 +6303,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>233</v>
       </c>
@@ -6275,7 +6353,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>234</v>
       </c>
@@ -6325,7 +6403,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>235</v>
       </c>
@@ -6375,7 +6453,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>236</v>
       </c>
@@ -6425,7 +6503,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>237</v>
       </c>
@@ -6475,7 +6553,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>238</v>
       </c>
@@ -6525,7 +6603,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>239</v>
       </c>
@@ -6575,7 +6653,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>240</v>
       </c>
@@ -6625,7 +6703,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>242</v>
       </c>
@@ -6675,7 +6753,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>243</v>
       </c>
@@ -6725,7 +6803,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>244</v>
       </c>
@@ -6775,7 +6853,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>245</v>
       </c>
@@ -6825,7 +6903,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>246</v>
       </c>
@@ -6875,7 +6953,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>247</v>
       </c>
@@ -6925,7 +7003,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>248</v>
       </c>
@@ -6969,7 +7047,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>132</v>
       </c>
@@ -7019,7 +7097,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>134</v>
       </c>
@@ -7069,7 +7147,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>135</v>
       </c>
@@ -7119,7 +7197,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>136</v>
       </c>
@@ -7169,7 +7247,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>252</v>
       </c>
@@ -7219,7 +7297,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>137</v>
       </c>
@@ -7269,7 +7347,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>138</v>
       </c>
@@ -7319,7 +7397,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>139</v>
       </c>
@@ -7369,7 +7447,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>140</v>
       </c>
@@ -7419,7 +7497,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>141</v>
       </c>
@@ -7469,7 +7547,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>142</v>
       </c>
@@ -7519,7 +7597,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>143</v>
       </c>
@@ -7569,7 +7647,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>144</v>
       </c>
@@ -7619,7 +7697,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>145</v>
       </c>
@@ -7669,7 +7747,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>146</v>
       </c>
@@ -7719,7 +7797,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>147</v>
       </c>
@@ -7769,7 +7847,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>148</v>
       </c>
@@ -7819,7 +7897,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>149</v>
       </c>
@@ -7869,7 +7947,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>150</v>
       </c>
@@ -7919,7 +7997,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>151</v>
       </c>
@@ -7969,7 +8047,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>152</v>
       </c>
@@ -8019,7 +8097,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>153</v>
       </c>
@@ -8069,7 +8147,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>154</v>
       </c>
@@ -8119,7 +8197,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>155</v>
       </c>
@@ -8169,7 +8247,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>156</v>
       </c>
@@ -8219,7 +8297,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>157</v>
       </c>
@@ -8269,7 +8347,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>158</v>
       </c>
@@ -8319,7 +8397,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>159</v>
       </c>
@@ -8369,7 +8447,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>160</v>
       </c>
@@ -8419,7 +8497,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>161</v>
       </c>
@@ -8469,7 +8547,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>162</v>
       </c>
@@ -8519,7 +8597,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>163</v>
       </c>
@@ -8569,7 +8647,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>164</v>
       </c>
@@ -8619,7 +8697,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>165</v>
       </c>
@@ -8669,7 +8747,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>166</v>
       </c>
@@ -8719,7 +8797,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>167</v>
       </c>
@@ -8769,7 +8847,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>168</v>
       </c>
@@ -8819,7 +8897,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>169</v>
       </c>
@@ -8869,7 +8947,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>170</v>
       </c>
@@ -8919,7 +8997,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>171</v>
       </c>
@@ -8969,7 +9047,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>172</v>
       </c>
@@ -9019,7 +9097,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>173</v>
       </c>
@@ -9069,7 +9147,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>174</v>
       </c>
@@ -9119,7 +9197,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>175</v>
       </c>
@@ -9169,7 +9247,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>176</v>
       </c>
@@ -9219,7 +9297,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>177</v>
       </c>
@@ -9269,7 +9347,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>178</v>
       </c>
@@ -9319,7 +9397,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>179</v>
       </c>
@@ -9369,7 +9447,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>180</v>
       </c>
@@ -9419,7 +9497,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>181</v>
       </c>
@@ -9469,7 +9547,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>182</v>
       </c>
@@ -9519,7 +9597,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>183</v>
       </c>
@@ -9569,7 +9647,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>184</v>
       </c>
@@ -9619,7 +9697,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>185</v>
       </c>
@@ -9669,7 +9747,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>186</v>
       </c>
@@ -9719,7 +9797,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>187</v>
       </c>
@@ -9769,7 +9847,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>188</v>
       </c>
@@ -9819,7 +9897,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>189</v>
       </c>
@@ -9869,7 +9947,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>190</v>
       </c>
@@ -9919,7 +9997,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>191</v>
       </c>
@@ -9969,7 +10047,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>253</v>
       </c>
@@ -10019,7 +10097,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>192</v>
       </c>
@@ -10069,7 +10147,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>193</v>
       </c>
@@ -10119,7 +10197,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>194</v>
       </c>
@@ -10169,7 +10247,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>195</v>
       </c>
@@ -10219,7 +10297,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>196</v>
       </c>
@@ -10269,7 +10347,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>197</v>
       </c>
@@ -10319,7 +10397,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>198</v>
       </c>
@@ -10369,7 +10447,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>199</v>
       </c>
@@ -10419,7 +10497,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>200</v>
       </c>
@@ -10469,7 +10547,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>201</v>
       </c>
@@ -10519,7 +10597,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>202</v>
       </c>
@@ -10569,7 +10647,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>203</v>
       </c>
@@ -10619,7 +10697,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>204</v>
       </c>
@@ -10669,7 +10747,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>205</v>
       </c>
@@ -10719,7 +10797,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>206</v>
       </c>
@@ -10769,7 +10847,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>207</v>
       </c>
@@ -10819,7 +10897,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>208</v>
       </c>
@@ -10869,7 +10947,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>209</v>
       </c>
@@ -10919,7 +10997,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>210</v>
       </c>
@@ -10969,7 +11047,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>211</v>
       </c>
@@ -11019,7 +11097,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>212</v>
       </c>
@@ -11069,7 +11147,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>213</v>
       </c>
@@ -11119,7 +11197,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>214</v>
       </c>
@@ -11169,7 +11247,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>215</v>
       </c>
@@ -11219,7 +11297,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>216</v>
       </c>
@@ -11269,7 +11347,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>217</v>
       </c>
@@ -11319,7 +11397,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>218</v>
       </c>
@@ -11369,7 +11447,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>219</v>
       </c>
@@ -11419,7 +11497,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>220</v>
       </c>
@@ -11469,7 +11547,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>221</v>
       </c>
@@ -11519,7 +11597,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>222</v>
       </c>
@@ -11569,7 +11647,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>223</v>
       </c>
@@ -11619,7 +11697,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>224</v>
       </c>
@@ -11669,7 +11747,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>225</v>
       </c>
@@ -11719,7 +11797,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>226</v>
       </c>
@@ -11769,7 +11847,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>227</v>
       </c>
@@ -11819,7 +11897,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>228</v>
       </c>
@@ -11869,7 +11947,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>229</v>
       </c>
@@ -11919,7 +11997,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>230</v>
       </c>
@@ -11969,7 +12047,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>231</v>
       </c>
@@ -12019,7 +12097,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>232</v>
       </c>
@@ -12069,7 +12147,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>233</v>
       </c>
@@ -12119,7 +12197,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>234</v>
       </c>
@@ -12169,7 +12247,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>235</v>
       </c>
@@ -12219,7 +12297,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>236</v>
       </c>
@@ -12269,7 +12347,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>237</v>
       </c>
@@ -12319,7 +12397,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>238</v>
       </c>
@@ -12369,7 +12447,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>239</v>
       </c>
@@ -12419,7 +12497,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>240</v>
       </c>
@@ -12469,7 +12547,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>242</v>
       </c>
@@ -12519,7 +12597,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>243</v>
       </c>
@@ -12569,7 +12647,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>244</v>
       </c>
@@ -12619,7 +12697,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>245</v>
       </c>
@@ -12669,7 +12747,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>246</v>
       </c>
@@ -12719,7 +12797,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>247</v>
       </c>
@@ -12769,7 +12847,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>248</v>
       </c>
@@ -12817,6 +12895,5856 @@
       </c>
       <c r="P233" s="1">
         <v>46054</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>139</v>
+      </c>
+      <c r="B234" t="s">
+        <v>26</v>
+      </c>
+      <c r="C234">
+        <v>852062</v>
+      </c>
+      <c r="D234" t="s">
+        <v>25</v>
+      </c>
+      <c r="E234" t="s">
+        <v>16</v>
+      </c>
+      <c r="F234" t="s">
+        <v>17</v>
+      </c>
+      <c r="G234">
+        <v>42</v>
+      </c>
+      <c r="H234">
+        <v>1</v>
+      </c>
+      <c r="I234">
+        <v>42</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234" s="2">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>42</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>0.97</v>
+      </c>
+      <c r="O234">
+        <v>0.46762731481481484</v>
+      </c>
+      <c r="P234" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>157</v>
+      </c>
+      <c r="B235" t="s">
+        <v>23</v>
+      </c>
+      <c r="C235">
+        <v>1114991</v>
+      </c>
+      <c r="D235" t="s">
+        <v>44</v>
+      </c>
+      <c r="E235" t="s">
+        <v>16</v>
+      </c>
+      <c r="F235" t="s">
+        <v>17</v>
+      </c>
+      <c r="G235">
+        <v>62</v>
+      </c>
+      <c r="H235">
+        <v>1</v>
+      </c>
+      <c r="I235">
+        <v>62</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235" s="2">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>62</v>
+      </c>
+      <c r="M235">
+        <v>0</v>
+      </c>
+      <c r="N235">
+        <v>0.94</v>
+      </c>
+      <c r="O235">
+        <v>0.48136574074074073</v>
+      </c>
+      <c r="P235" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>153</v>
+      </c>
+      <c r="B236" t="s">
+        <v>19</v>
+      </c>
+      <c r="C236">
+        <v>1081616</v>
+      </c>
+      <c r="D236" t="s">
+        <v>40</v>
+      </c>
+      <c r="E236" t="s">
+        <v>16</v>
+      </c>
+      <c r="F236" t="s">
+        <v>17</v>
+      </c>
+      <c r="G236">
+        <v>62</v>
+      </c>
+      <c r="H236">
+        <v>1</v>
+      </c>
+      <c r="I236">
+        <v>62</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236" s="2">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>62</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>0.95</v>
+      </c>
+      <c r="O236">
+        <v>0.24810185185185185</v>
+      </c>
+      <c r="P236" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>197</v>
+      </c>
+      <c r="B237" t="s">
+        <v>30</v>
+      </c>
+      <c r="C237">
+        <v>1426096</v>
+      </c>
+      <c r="D237" t="s">
+        <v>64</v>
+      </c>
+      <c r="E237" t="s">
+        <v>16</v>
+      </c>
+      <c r="F237" t="s">
+        <v>17</v>
+      </c>
+      <c r="G237">
+        <v>26</v>
+      </c>
+      <c r="H237">
+        <v>1</v>
+      </c>
+      <c r="I237">
+        <v>26</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237" s="2">
+        <v>1</v>
+      </c>
+      <c r="L237">
+        <v>26</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>0.96</v>
+      </c>
+      <c r="O237">
+        <v>0.11520833333333334</v>
+      </c>
+      <c r="P237" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>177</v>
+      </c>
+      <c r="B238" t="s">
+        <v>23</v>
+      </c>
+      <c r="C238">
+        <v>1399803</v>
+      </c>
+      <c r="D238" t="s">
+        <v>64</v>
+      </c>
+      <c r="E238" t="s">
+        <v>16</v>
+      </c>
+      <c r="F238" t="s">
+        <v>17</v>
+      </c>
+      <c r="G238">
+        <v>39</v>
+      </c>
+      <c r="H238">
+        <v>1</v>
+      </c>
+      <c r="I238">
+        <v>39</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238" s="2">
+        <v>1</v>
+      </c>
+      <c r="L238">
+        <v>39</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>0.94</v>
+      </c>
+      <c r="O238">
+        <v>0.1948263888888889</v>
+      </c>
+      <c r="P238" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>178</v>
+      </c>
+      <c r="B239" t="s">
+        <v>26</v>
+      </c>
+      <c r="C239">
+        <v>1402939</v>
+      </c>
+      <c r="D239" t="s">
+        <v>65</v>
+      </c>
+      <c r="E239" t="s">
+        <v>16</v>
+      </c>
+      <c r="F239" t="s">
+        <v>17</v>
+      </c>
+      <c r="G239">
+        <v>50</v>
+      </c>
+      <c r="H239">
+        <v>0.98</v>
+      </c>
+      <c r="I239">
+        <v>49</v>
+      </c>
+      <c r="J239">
+        <v>1</v>
+      </c>
+      <c r="K239" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="L239">
+        <v>49</v>
+      </c>
+      <c r="M239">
+        <v>0</v>
+      </c>
+      <c r="N239">
+        <v>0.96</v>
+      </c>
+      <c r="O239">
+        <v>0.23715277777777777</v>
+      </c>
+      <c r="P239" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>136</v>
+      </c>
+      <c r="B240" t="s">
+        <v>133</v>
+      </c>
+      <c r="C240">
+        <v>845244</v>
+      </c>
+      <c r="D240" t="s">
+        <v>21</v>
+      </c>
+      <c r="E240" t="s">
+        <v>16</v>
+      </c>
+      <c r="F240" t="s">
+        <v>17</v>
+      </c>
+      <c r="G240">
+        <v>62</v>
+      </c>
+      <c r="H240">
+        <v>1</v>
+      </c>
+      <c r="I240">
+        <v>62</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240" s="2">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>62</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>0.92</v>
+      </c>
+      <c r="O240">
+        <v>0.40864583333333332</v>
+      </c>
+      <c r="P240" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>147</v>
+      </c>
+      <c r="B241" t="s">
+        <v>23</v>
+      </c>
+      <c r="C241">
+        <v>866201</v>
+      </c>
+      <c r="D241" t="s">
+        <v>34</v>
+      </c>
+      <c r="E241" t="s">
+        <v>16</v>
+      </c>
+      <c r="F241" t="s">
+        <v>17</v>
+      </c>
+      <c r="G241">
+        <v>42</v>
+      </c>
+      <c r="H241">
+        <v>1</v>
+      </c>
+      <c r="I241">
+        <v>42</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241" s="2">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>42</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>0.96</v>
+      </c>
+      <c r="O241">
+        <v>0.2409259259259259</v>
+      </c>
+      <c r="P241" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>193</v>
+      </c>
+      <c r="B242" t="s">
+        <v>26</v>
+      </c>
+      <c r="C242">
+        <v>1422272</v>
+      </c>
+      <c r="D242" t="s">
+        <v>79</v>
+      </c>
+      <c r="E242" t="s">
+        <v>16</v>
+      </c>
+      <c r="F242" t="s">
+        <v>17</v>
+      </c>
+      <c r="G242">
+        <v>37</v>
+      </c>
+      <c r="H242">
+        <v>1</v>
+      </c>
+      <c r="I242">
+        <v>37</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242" s="2">
+        <v>1</v>
+      </c>
+      <c r="L242">
+        <v>37</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>0.95</v>
+      </c>
+      <c r="O242">
+        <v>0.15930555555555556</v>
+      </c>
+      <c r="P242" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>229</v>
+      </c>
+      <c r="B243" t="s">
+        <v>19</v>
+      </c>
+      <c r="C243">
+        <v>1442353</v>
+      </c>
+      <c r="D243" t="s">
+        <v>114</v>
+      </c>
+      <c r="E243" t="s">
+        <v>16</v>
+      </c>
+      <c r="F243" t="s">
+        <v>17</v>
+      </c>
+      <c r="G243">
+        <v>18</v>
+      </c>
+      <c r="H243">
+        <v>1</v>
+      </c>
+      <c r="I243">
+        <v>18</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243" s="2">
+        <v>1</v>
+      </c>
+      <c r="L243">
+        <v>18</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
+      </c>
+      <c r="N243">
+        <v>1</v>
+      </c>
+      <c r="O243">
+        <v>0.24162037037037035</v>
+      </c>
+      <c r="P243" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>267</v>
+      </c>
+      <c r="B244" t="s">
+        <v>30</v>
+      </c>
+      <c r="C244">
+        <v>840829</v>
+      </c>
+      <c r="D244" t="s">
+        <v>254</v>
+      </c>
+      <c r="E244" t="s">
+        <v>16</v>
+      </c>
+      <c r="F244" t="s">
+        <v>17</v>
+      </c>
+      <c r="G244">
+        <v>62</v>
+      </c>
+      <c r="H244">
+        <v>1</v>
+      </c>
+      <c r="I244">
+        <v>62</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244" s="2">
+        <v>1</v>
+      </c>
+      <c r="L244">
+        <v>62</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
+      </c>
+      <c r="N244">
+        <v>0.96</v>
+      </c>
+      <c r="O244">
+        <v>0.3382175925925926</v>
+      </c>
+      <c r="P244" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>168</v>
+      </c>
+      <c r="B245" t="s">
+        <v>26</v>
+      </c>
+      <c r="C245">
+        <v>1150499</v>
+      </c>
+      <c r="D245" t="s">
+        <v>55</v>
+      </c>
+      <c r="E245" t="s">
+        <v>16</v>
+      </c>
+      <c r="F245" t="s">
+        <v>17</v>
+      </c>
+      <c r="G245">
+        <v>62</v>
+      </c>
+      <c r="H245">
+        <v>1</v>
+      </c>
+      <c r="I245">
+        <v>62</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245" s="2">
+        <v>1</v>
+      </c>
+      <c r="L245">
+        <v>62</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>0.95</v>
+      </c>
+      <c r="O245">
+        <v>0.24878472222222223</v>
+      </c>
+      <c r="P245" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>224</v>
+      </c>
+      <c r="B246" t="s">
+        <v>26</v>
+      </c>
+      <c r="C246">
+        <v>1442179</v>
+      </c>
+      <c r="D246" t="s">
+        <v>109</v>
+      </c>
+      <c r="E246" t="s">
+        <v>16</v>
+      </c>
+      <c r="F246" t="s">
+        <v>17</v>
+      </c>
+      <c r="G246">
+        <v>20</v>
+      </c>
+      <c r="H246">
+        <v>1</v>
+      </c>
+      <c r="I246">
+        <v>20</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246" s="2">
+        <v>1</v>
+      </c>
+      <c r="L246">
+        <v>20</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>1</v>
+      </c>
+      <c r="O246">
+        <v>9.8125000000000004E-2</v>
+      </c>
+      <c r="P246" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>176</v>
+      </c>
+      <c r="B247" t="s">
+        <v>26</v>
+      </c>
+      <c r="C247">
+        <v>1400359</v>
+      </c>
+      <c r="D247" t="s">
+        <v>63</v>
+      </c>
+      <c r="E247" t="s">
+        <v>16</v>
+      </c>
+      <c r="F247" t="s">
+        <v>17</v>
+      </c>
+      <c r="G247">
+        <v>61</v>
+      </c>
+      <c r="H247">
+        <v>1</v>
+      </c>
+      <c r="I247">
+        <v>61</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247" s="2">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>61</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>0.97</v>
+      </c>
+      <c r="O247">
+        <v>0.29245370370370372</v>
+      </c>
+      <c r="P247" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>155</v>
+      </c>
+      <c r="B248" t="s">
+        <v>30</v>
+      </c>
+      <c r="C248">
+        <v>1104311</v>
+      </c>
+      <c r="D248" t="s">
+        <v>42</v>
+      </c>
+      <c r="E248" t="s">
+        <v>16</v>
+      </c>
+      <c r="F248" t="s">
+        <v>17</v>
+      </c>
+      <c r="G248">
+        <v>62</v>
+      </c>
+      <c r="H248">
+        <v>1</v>
+      </c>
+      <c r="I248">
+        <v>62</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248" s="2">
+        <v>1</v>
+      </c>
+      <c r="L248">
+        <v>62</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>0.95</v>
+      </c>
+      <c r="O248">
+        <v>0.37177083333333333</v>
+      </c>
+      <c r="P248" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249" t="s">
+        <v>26</v>
+      </c>
+      <c r="C249">
+        <v>845604</v>
+      </c>
+      <c r="D249" t="s">
+        <v>250</v>
+      </c>
+      <c r="E249" t="s">
+        <v>16</v>
+      </c>
+      <c r="F249" t="s">
+        <v>17</v>
+      </c>
+      <c r="G249">
+        <v>40</v>
+      </c>
+      <c r="H249">
+        <v>1</v>
+      </c>
+      <c r="I249">
+        <v>40</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249" s="2">
+        <v>1</v>
+      </c>
+      <c r="L249">
+        <v>40</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>0.95</v>
+      </c>
+      <c r="O249">
+        <v>0.35625000000000001</v>
+      </c>
+      <c r="P249" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>180</v>
+      </c>
+      <c r="B250" t="s">
+        <v>26</v>
+      </c>
+      <c r="C250">
+        <v>1404784</v>
+      </c>
+      <c r="D250" t="s">
+        <v>67</v>
+      </c>
+      <c r="E250" t="s">
+        <v>16</v>
+      </c>
+      <c r="F250" t="s">
+        <v>17</v>
+      </c>
+      <c r="G250">
+        <v>52</v>
+      </c>
+      <c r="H250">
+        <v>1</v>
+      </c>
+      <c r="I250">
+        <v>52</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250" s="2">
+        <v>1</v>
+      </c>
+      <c r="L250">
+        <v>52</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>0.95</v>
+      </c>
+      <c r="O250">
+        <v>0.25491898148148145</v>
+      </c>
+      <c r="P250" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>192</v>
+      </c>
+      <c r="B251" t="s">
+        <v>23</v>
+      </c>
+      <c r="C251">
+        <v>1420400</v>
+      </c>
+      <c r="D251" t="s">
+        <v>78</v>
+      </c>
+      <c r="E251" t="s">
+        <v>16</v>
+      </c>
+      <c r="F251" t="s">
+        <v>17</v>
+      </c>
+      <c r="G251">
+        <v>27</v>
+      </c>
+      <c r="H251">
+        <v>1</v>
+      </c>
+      <c r="I251">
+        <v>27</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251" s="2">
+        <v>1</v>
+      </c>
+      <c r="L251">
+        <v>27</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>0.94</v>
+      </c>
+      <c r="O251">
+        <v>0.11805555555555557</v>
+      </c>
+      <c r="P251" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>138</v>
+      </c>
+      <c r="B252" t="s">
+        <v>26</v>
+      </c>
+      <c r="C252">
+        <v>848928</v>
+      </c>
+      <c r="D252" t="s">
+        <v>24</v>
+      </c>
+      <c r="E252" t="s">
+        <v>16</v>
+      </c>
+      <c r="F252" t="s">
+        <v>17</v>
+      </c>
+      <c r="G252">
+        <v>42</v>
+      </c>
+      <c r="H252">
+        <v>1</v>
+      </c>
+      <c r="I252">
+        <v>42</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252" s="2">
+        <v>1</v>
+      </c>
+      <c r="L252">
+        <v>42</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>0.95</v>
+      </c>
+      <c r="O252">
+        <v>0.20783564814814814</v>
+      </c>
+      <c r="P252" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>234</v>
+      </c>
+      <c r="B253" t="s">
+        <v>26</v>
+      </c>
+      <c r="C253">
+        <v>1444008</v>
+      </c>
+      <c r="D253" t="s">
+        <v>118</v>
+      </c>
+      <c r="E253" t="s">
+        <v>16</v>
+      </c>
+      <c r="F253" t="s">
+        <v>17</v>
+      </c>
+      <c r="G253">
+        <v>19</v>
+      </c>
+      <c r="H253">
+        <v>1</v>
+      </c>
+      <c r="I253">
+        <v>19</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253" s="2">
+        <v>1</v>
+      </c>
+      <c r="L253">
+        <v>19</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>0.99</v>
+      </c>
+      <c r="O253">
+        <v>6.8182870370370366E-2</v>
+      </c>
+      <c r="P253" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>223</v>
+      </c>
+      <c r="B254" t="s">
+        <v>30</v>
+      </c>
+      <c r="C254">
+        <v>1442176</v>
+      </c>
+      <c r="D254" t="s">
+        <v>108</v>
+      </c>
+      <c r="E254" t="s">
+        <v>16</v>
+      </c>
+      <c r="F254" t="s">
+        <v>17</v>
+      </c>
+      <c r="G254">
+        <v>20</v>
+      </c>
+      <c r="H254">
+        <v>0.95</v>
+      </c>
+      <c r="I254">
+        <v>19</v>
+      </c>
+      <c r="J254">
+        <v>1</v>
+      </c>
+      <c r="K254" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L254">
+        <v>19</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>0.99</v>
+      </c>
+      <c r="O254">
+        <v>0.53634259259259254</v>
+      </c>
+      <c r="P254" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>244</v>
+      </c>
+      <c r="B255" t="s">
+        <v>30</v>
+      </c>
+      <c r="C255">
+        <v>1444314</v>
+      </c>
+      <c r="D255" t="s">
+        <v>127</v>
+      </c>
+      <c r="E255" t="s">
+        <v>16</v>
+      </c>
+      <c r="F255" t="s">
+        <v>17</v>
+      </c>
+      <c r="G255">
+        <v>19</v>
+      </c>
+      <c r="H255">
+        <v>1</v>
+      </c>
+      <c r="I255">
+        <v>19</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255" s="2">
+        <v>1</v>
+      </c>
+      <c r="L255">
+        <v>19</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>0.99</v>
+      </c>
+      <c r="O255">
+        <v>0.12194444444444445</v>
+      </c>
+      <c r="P255" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>228</v>
+      </c>
+      <c r="B256" t="s">
+        <v>30</v>
+      </c>
+      <c r="C256">
+        <v>1442349</v>
+      </c>
+      <c r="D256" t="s">
+        <v>113</v>
+      </c>
+      <c r="E256" t="s">
+        <v>16</v>
+      </c>
+      <c r="F256" t="s">
+        <v>17</v>
+      </c>
+      <c r="G256">
+        <v>24</v>
+      </c>
+      <c r="H256">
+        <v>1</v>
+      </c>
+      <c r="I256">
+        <v>24</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256" s="2">
+        <v>1</v>
+      </c>
+      <c r="L256">
+        <v>24</v>
+      </c>
+      <c r="M256">
+        <v>0</v>
+      </c>
+      <c r="N256">
+        <v>0.97</v>
+      </c>
+      <c r="O256">
+        <v>0.15341435185185184</v>
+      </c>
+      <c r="P256" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>203</v>
+      </c>
+      <c r="B257" t="s">
+        <v>30</v>
+      </c>
+      <c r="C257">
+        <v>1429587</v>
+      </c>
+      <c r="D257" t="s">
+        <v>88</v>
+      </c>
+      <c r="E257" t="s">
+        <v>16</v>
+      </c>
+      <c r="F257" t="s">
+        <v>17</v>
+      </c>
+      <c r="G257">
+        <v>44</v>
+      </c>
+      <c r="H257">
+        <v>1</v>
+      </c>
+      <c r="I257">
+        <v>44</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257" s="2">
+        <v>1</v>
+      </c>
+      <c r="L257">
+        <v>44</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>0.98</v>
+      </c>
+      <c r="O257">
+        <v>0.35129629629629627</v>
+      </c>
+      <c r="P257" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>242</v>
+      </c>
+      <c r="B258" t="s">
+        <v>26</v>
+      </c>
+      <c r="C258">
+        <v>1444312</v>
+      </c>
+      <c r="D258" t="s">
+        <v>125</v>
+      </c>
+      <c r="E258" t="s">
+        <v>16</v>
+      </c>
+      <c r="F258" t="s">
+        <v>17</v>
+      </c>
+      <c r="G258">
+        <v>19</v>
+      </c>
+      <c r="H258">
+        <v>1</v>
+      </c>
+      <c r="I258">
+        <v>19</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258" s="2">
+        <v>1</v>
+      </c>
+      <c r="L258">
+        <v>19</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
+      </c>
+      <c r="N258">
+        <v>0.93</v>
+      </c>
+      <c r="O258">
+        <v>8.6793981481481486E-2</v>
+      </c>
+      <c r="P258" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>213</v>
+      </c>
+      <c r="B259" t="s">
+        <v>23</v>
+      </c>
+      <c r="C259">
+        <v>1441955</v>
+      </c>
+      <c r="D259" t="s">
+        <v>98</v>
+      </c>
+      <c r="E259" t="s">
+        <v>16</v>
+      </c>
+      <c r="F259" t="s">
+        <v>17</v>
+      </c>
+      <c r="G259">
+        <v>24</v>
+      </c>
+      <c r="H259">
+        <v>0.96</v>
+      </c>
+      <c r="I259">
+        <v>23</v>
+      </c>
+      <c r="J259">
+        <v>1</v>
+      </c>
+      <c r="K259" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="L259">
+        <v>23</v>
+      </c>
+      <c r="M259">
+        <v>0</v>
+      </c>
+      <c r="N259">
+        <v>0.99</v>
+      </c>
+      <c r="O259">
+        <v>0.32855324074074072</v>
+      </c>
+      <c r="P259" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>171</v>
+      </c>
+      <c r="B260" t="s">
+        <v>30</v>
+      </c>
+      <c r="C260">
+        <v>1391323</v>
+      </c>
+      <c r="D260" t="s">
+        <v>58</v>
+      </c>
+      <c r="E260" t="s">
+        <v>16</v>
+      </c>
+      <c r="F260" t="s">
+        <v>17</v>
+      </c>
+      <c r="G260">
+        <v>62</v>
+      </c>
+      <c r="H260">
+        <v>1</v>
+      </c>
+      <c r="I260">
+        <v>62</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260" s="2">
+        <v>1</v>
+      </c>
+      <c r="L260">
+        <v>62</v>
+      </c>
+      <c r="M260">
+        <v>0</v>
+      </c>
+      <c r="N260">
+        <v>0.95</v>
+      </c>
+      <c r="O260">
+        <v>0.28225694444444444</v>
+      </c>
+      <c r="P260" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>222</v>
+      </c>
+      <c r="B261" t="s">
+        <v>23</v>
+      </c>
+      <c r="C261">
+        <v>1442173</v>
+      </c>
+      <c r="D261" t="s">
+        <v>107</v>
+      </c>
+      <c r="E261" t="s">
+        <v>16</v>
+      </c>
+      <c r="F261" t="s">
+        <v>17</v>
+      </c>
+      <c r="G261">
+        <v>23</v>
+      </c>
+      <c r="H261">
+        <v>1</v>
+      </c>
+      <c r="I261">
+        <v>23</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261" s="2">
+        <v>1</v>
+      </c>
+      <c r="L261">
+        <v>23</v>
+      </c>
+      <c r="M261">
+        <v>0</v>
+      </c>
+      <c r="N261">
+        <v>0.99</v>
+      </c>
+      <c r="O261">
+        <v>0.17646990740740742</v>
+      </c>
+      <c r="P261" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>159</v>
+      </c>
+      <c r="B262" t="s">
+        <v>26</v>
+      </c>
+      <c r="C262">
+        <v>1137263</v>
+      </c>
+      <c r="D262" t="s">
+        <v>46</v>
+      </c>
+      <c r="E262" t="s">
+        <v>16</v>
+      </c>
+      <c r="F262" t="s">
+        <v>17</v>
+      </c>
+      <c r="G262">
+        <v>62</v>
+      </c>
+      <c r="H262">
+        <v>1</v>
+      </c>
+      <c r="I262">
+        <v>62</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262" s="2">
+        <v>1</v>
+      </c>
+      <c r="L262">
+        <v>62</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
+        <v>0.94</v>
+      </c>
+      <c r="O262">
+        <v>0.25223379629629633</v>
+      </c>
+      <c r="P262" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>191</v>
+      </c>
+      <c r="B263" t="s">
+        <v>26</v>
+      </c>
+      <c r="C263">
+        <v>1419988</v>
+      </c>
+      <c r="D263" t="s">
+        <v>77</v>
+      </c>
+      <c r="E263" t="s">
+        <v>16</v>
+      </c>
+      <c r="F263" t="s">
+        <v>17</v>
+      </c>
+      <c r="G263">
+        <v>59</v>
+      </c>
+      <c r="H263">
+        <v>1</v>
+      </c>
+      <c r="I263">
+        <v>59</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263" s="2">
+        <v>1</v>
+      </c>
+      <c r="L263">
+        <v>59</v>
+      </c>
+      <c r="M263">
+        <v>0</v>
+      </c>
+      <c r="N263">
+        <v>0.97</v>
+      </c>
+      <c r="O263">
+        <v>0.46549768518518514</v>
+      </c>
+      <c r="P263" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>151</v>
+      </c>
+      <c r="B264" t="s">
+        <v>26</v>
+      </c>
+      <c r="C264">
+        <v>1028931</v>
+      </c>
+      <c r="D264" t="s">
+        <v>38</v>
+      </c>
+      <c r="E264" t="s">
+        <v>16</v>
+      </c>
+      <c r="F264" t="s">
+        <v>17</v>
+      </c>
+      <c r="G264">
+        <v>25</v>
+      </c>
+      <c r="H264">
+        <v>0.96</v>
+      </c>
+      <c r="I264">
+        <v>24</v>
+      </c>
+      <c r="J264">
+        <v>1</v>
+      </c>
+      <c r="K264" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="L264">
+        <v>24</v>
+      </c>
+      <c r="M264">
+        <v>0</v>
+      </c>
+      <c r="N264">
+        <v>0.99</v>
+      </c>
+      <c r="O264">
+        <v>0.13716435185185186</v>
+      </c>
+      <c r="P264" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>236</v>
+      </c>
+      <c r="B265" t="s">
+        <v>26</v>
+      </c>
+      <c r="C265">
+        <v>1444029</v>
+      </c>
+      <c r="D265" t="s">
+        <v>120</v>
+      </c>
+      <c r="E265" t="s">
+        <v>16</v>
+      </c>
+      <c r="F265" t="s">
+        <v>17</v>
+      </c>
+      <c r="G265">
+        <v>19</v>
+      </c>
+      <c r="H265">
+        <v>1</v>
+      </c>
+      <c r="I265">
+        <v>19</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+      <c r="K265" s="2">
+        <v>1</v>
+      </c>
+      <c r="L265">
+        <v>19</v>
+      </c>
+      <c r="M265">
+        <v>0</v>
+      </c>
+      <c r="N265">
+        <v>0.99</v>
+      </c>
+      <c r="O265">
+        <v>6.4895833333333333E-2</v>
+      </c>
+      <c r="P265" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>143</v>
+      </c>
+      <c r="B266" t="s">
+        <v>19</v>
+      </c>
+      <c r="C266">
+        <v>862061</v>
+      </c>
+      <c r="D266" t="s">
+        <v>29</v>
+      </c>
+      <c r="E266" t="s">
+        <v>16</v>
+      </c>
+      <c r="F266" t="s">
+        <v>17</v>
+      </c>
+      <c r="G266">
+        <v>52</v>
+      </c>
+      <c r="H266">
+        <v>1</v>
+      </c>
+      <c r="I266">
+        <v>52</v>
+      </c>
+      <c r="J266">
+        <v>0</v>
+      </c>
+      <c r="K266" s="2">
+        <v>1</v>
+      </c>
+      <c r="L266">
+        <v>52</v>
+      </c>
+      <c r="M266">
+        <v>0</v>
+      </c>
+      <c r="N266">
+        <v>0.94</v>
+      </c>
+      <c r="O266">
+        <v>0.33650462962962963</v>
+      </c>
+      <c r="P266" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>142</v>
+      </c>
+      <c r="B267" t="s">
+        <v>30</v>
+      </c>
+      <c r="C267">
+        <v>861415</v>
+      </c>
+      <c r="D267" t="s">
+        <v>29</v>
+      </c>
+      <c r="E267" t="s">
+        <v>16</v>
+      </c>
+      <c r="F267" t="s">
+        <v>17</v>
+      </c>
+      <c r="G267">
+        <v>32</v>
+      </c>
+      <c r="H267">
+        <v>1</v>
+      </c>
+      <c r="I267">
+        <v>32</v>
+      </c>
+      <c r="J267">
+        <v>0</v>
+      </c>
+      <c r="K267" s="2">
+        <v>1</v>
+      </c>
+      <c r="L267">
+        <v>32</v>
+      </c>
+      <c r="M267">
+        <v>0</v>
+      </c>
+      <c r="N267">
+        <v>0.96</v>
+      </c>
+      <c r="O267">
+        <v>0.15697916666666667</v>
+      </c>
+      <c r="P267" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>184</v>
+      </c>
+      <c r="B268" t="s">
+        <v>23</v>
+      </c>
+      <c r="C268">
+        <v>1409450</v>
+      </c>
+      <c r="D268" t="s">
+        <v>71</v>
+      </c>
+      <c r="E268" t="s">
+        <v>16</v>
+      </c>
+      <c r="F268" t="s">
+        <v>17</v>
+      </c>
+      <c r="G268">
+        <v>39</v>
+      </c>
+      <c r="H268">
+        <v>1</v>
+      </c>
+      <c r="I268">
+        <v>39</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268" s="2">
+        <v>1</v>
+      </c>
+      <c r="L268">
+        <v>39</v>
+      </c>
+      <c r="M268">
+        <v>0</v>
+      </c>
+      <c r="N268">
+        <v>0.93</v>
+      </c>
+      <c r="O268">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="P268" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>209</v>
+      </c>
+      <c r="B269" t="s">
+        <v>26</v>
+      </c>
+      <c r="C269">
+        <v>1440114</v>
+      </c>
+      <c r="D269" t="s">
+        <v>94</v>
+      </c>
+      <c r="E269" t="s">
+        <v>16</v>
+      </c>
+      <c r="F269" t="s">
+        <v>17</v>
+      </c>
+      <c r="G269">
+        <v>22</v>
+      </c>
+      <c r="H269">
+        <v>1</v>
+      </c>
+      <c r="I269">
+        <v>22</v>
+      </c>
+      <c r="J269">
+        <v>0</v>
+      </c>
+      <c r="K269" s="2">
+        <v>1</v>
+      </c>
+      <c r="L269">
+        <v>22</v>
+      </c>
+      <c r="M269">
+        <v>0</v>
+      </c>
+      <c r="N269">
+        <v>0.95</v>
+      </c>
+      <c r="O269">
+        <v>0.13929398148148148</v>
+      </c>
+      <c r="P269" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>146</v>
+      </c>
+      <c r="B270" t="s">
+        <v>26</v>
+      </c>
+      <c r="C270">
+        <v>864510</v>
+      </c>
+      <c r="D270" t="s">
+        <v>33</v>
+      </c>
+      <c r="E270" t="s">
+        <v>16</v>
+      </c>
+      <c r="F270" t="s">
+        <v>17</v>
+      </c>
+      <c r="G270">
+        <v>22</v>
+      </c>
+      <c r="H270">
+        <v>1</v>
+      </c>
+      <c r="I270">
+        <v>22</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270" s="2">
+        <v>1</v>
+      </c>
+      <c r="L270">
+        <v>22</v>
+      </c>
+      <c r="M270">
+        <v>0</v>
+      </c>
+      <c r="N270">
+        <v>0.91</v>
+      </c>
+      <c r="O270">
+        <v>0.1095138888888889</v>
+      </c>
+      <c r="P270" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>182</v>
+      </c>
+      <c r="B271" t="s">
+        <v>26</v>
+      </c>
+      <c r="C271">
+        <v>1408475</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" t="s">
+        <v>16</v>
+      </c>
+      <c r="F271" t="s">
+        <v>17</v>
+      </c>
+      <c r="G271">
+        <v>85</v>
+      </c>
+      <c r="H271">
+        <v>1</v>
+      </c>
+      <c r="I271">
+        <v>85</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271" s="2">
+        <v>1</v>
+      </c>
+      <c r="L271">
+        <v>85</v>
+      </c>
+      <c r="M271">
+        <v>0</v>
+      </c>
+      <c r="N271">
+        <v>0.94</v>
+      </c>
+      <c r="O271">
+        <v>0.60410879629629632</v>
+      </c>
+      <c r="P271" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>160</v>
+      </c>
+      <c r="B272" t="s">
+        <v>23</v>
+      </c>
+      <c r="C272">
+        <v>1145386</v>
+      </c>
+      <c r="D272" t="s">
+        <v>47</v>
+      </c>
+      <c r="E272" t="s">
+        <v>16</v>
+      </c>
+      <c r="F272" t="s">
+        <v>17</v>
+      </c>
+      <c r="G272">
+        <v>61</v>
+      </c>
+      <c r="H272">
+        <v>1</v>
+      </c>
+      <c r="I272">
+        <v>61</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272" s="2">
+        <v>1</v>
+      </c>
+      <c r="L272">
+        <v>61</v>
+      </c>
+      <c r="M272">
+        <v>0</v>
+      </c>
+      <c r="N272">
+        <v>0.96</v>
+      </c>
+      <c r="O272">
+        <v>0.41184027777777782</v>
+      </c>
+      <c r="P272" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>200</v>
+      </c>
+      <c r="B273" t="s">
+        <v>30</v>
+      </c>
+      <c r="C273">
+        <v>1428179</v>
+      </c>
+      <c r="D273" t="s">
+        <v>85</v>
+      </c>
+      <c r="E273" t="s">
+        <v>16</v>
+      </c>
+      <c r="F273" t="s">
+        <v>17</v>
+      </c>
+      <c r="G273">
+        <v>24</v>
+      </c>
+      <c r="H273">
+        <v>1</v>
+      </c>
+      <c r="I273">
+        <v>24</v>
+      </c>
+      <c r="J273">
+        <v>0</v>
+      </c>
+      <c r="K273" s="2">
+        <v>1</v>
+      </c>
+      <c r="L273">
+        <v>24</v>
+      </c>
+      <c r="M273">
+        <v>0</v>
+      </c>
+      <c r="N273">
+        <v>0.95</v>
+      </c>
+      <c r="O273">
+        <v>0.12831018518518519</v>
+      </c>
+      <c r="P273" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>172</v>
+      </c>
+      <c r="B274" t="s">
+        <v>23</v>
+      </c>
+      <c r="C274">
+        <v>1391325</v>
+      </c>
+      <c r="D274" t="s">
+        <v>59</v>
+      </c>
+      <c r="E274" t="s">
+        <v>16</v>
+      </c>
+      <c r="F274" t="s">
+        <v>17</v>
+      </c>
+      <c r="G274">
+        <v>62</v>
+      </c>
+      <c r="H274">
+        <v>1</v>
+      </c>
+      <c r="I274">
+        <v>62</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274" s="2">
+        <v>1</v>
+      </c>
+      <c r="L274">
+        <v>62</v>
+      </c>
+      <c r="M274">
+        <v>0</v>
+      </c>
+      <c r="N274">
+        <v>0.96</v>
+      </c>
+      <c r="O274">
+        <v>0.23827546296296295</v>
+      </c>
+      <c r="P274" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>227</v>
+      </c>
+      <c r="B275" t="s">
+        <v>30</v>
+      </c>
+      <c r="C275">
+        <v>1442343</v>
+      </c>
+      <c r="D275" t="s">
+        <v>112</v>
+      </c>
+      <c r="E275" t="s">
+        <v>16</v>
+      </c>
+      <c r="F275" t="s">
+        <v>17</v>
+      </c>
+      <c r="G275">
+        <v>24</v>
+      </c>
+      <c r="H275">
+        <v>1</v>
+      </c>
+      <c r="I275">
+        <v>24</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275" s="2">
+        <v>1</v>
+      </c>
+      <c r="L275">
+        <v>24</v>
+      </c>
+      <c r="M275">
+        <v>0</v>
+      </c>
+      <c r="N275">
+        <v>0.91</v>
+      </c>
+      <c r="O275">
+        <v>0.19145833333333331</v>
+      </c>
+      <c r="P275" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>247</v>
+      </c>
+      <c r="B276" t="s">
+        <v>30</v>
+      </c>
+      <c r="C276">
+        <v>1444814</v>
+      </c>
+      <c r="D276" t="s">
+        <v>130</v>
+      </c>
+      <c r="E276" t="s">
+        <v>16</v>
+      </c>
+      <c r="F276" t="s">
+        <v>17</v>
+      </c>
+      <c r="G276">
+        <v>22</v>
+      </c>
+      <c r="H276">
+        <v>1</v>
+      </c>
+      <c r="I276">
+        <v>22</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276" s="2">
+        <v>1</v>
+      </c>
+      <c r="L276">
+        <v>22</v>
+      </c>
+      <c r="M276">
+        <v>0</v>
+      </c>
+      <c r="N276">
+        <v>0.98</v>
+      </c>
+      <c r="O276">
+        <v>0.22956018518518517</v>
+      </c>
+      <c r="P276" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>154</v>
+      </c>
+      <c r="B277" t="s">
+        <v>23</v>
+      </c>
+      <c r="C277">
+        <v>1081666</v>
+      </c>
+      <c r="D277" t="s">
+        <v>41</v>
+      </c>
+      <c r="E277" t="s">
+        <v>16</v>
+      </c>
+      <c r="F277" t="s">
+        <v>17</v>
+      </c>
+      <c r="G277">
+        <v>62</v>
+      </c>
+      <c r="H277">
+        <v>1</v>
+      </c>
+      <c r="I277">
+        <v>62</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277" s="2">
+        <v>1</v>
+      </c>
+      <c r="L277">
+        <v>62</v>
+      </c>
+      <c r="M277">
+        <v>0</v>
+      </c>
+      <c r="N277">
+        <v>0.97</v>
+      </c>
+      <c r="O277">
+        <v>0.26543981481481482</v>
+      </c>
+      <c r="P277" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>221</v>
+      </c>
+      <c r="B278" t="s">
+        <v>23</v>
+      </c>
+      <c r="C278">
+        <v>1442160</v>
+      </c>
+      <c r="D278" t="s">
+        <v>106</v>
+      </c>
+      <c r="E278" t="s">
+        <v>16</v>
+      </c>
+      <c r="F278" t="s">
+        <v>17</v>
+      </c>
+      <c r="G278">
+        <v>31</v>
+      </c>
+      <c r="H278">
+        <v>1</v>
+      </c>
+      <c r="I278">
+        <v>31</v>
+      </c>
+      <c r="J278">
+        <v>0</v>
+      </c>
+      <c r="K278" s="2">
+        <v>1</v>
+      </c>
+      <c r="L278">
+        <v>31</v>
+      </c>
+      <c r="M278">
+        <v>0</v>
+      </c>
+      <c r="N278">
+        <v>0.94</v>
+      </c>
+      <c r="O278">
+        <v>0.22771990740740741</v>
+      </c>
+      <c r="P278" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>148</v>
+      </c>
+      <c r="B279" t="s">
+        <v>26</v>
+      </c>
+      <c r="C279">
+        <v>866444</v>
+      </c>
+      <c r="D279" t="s">
+        <v>35</v>
+      </c>
+      <c r="E279" t="s">
+        <v>16</v>
+      </c>
+      <c r="F279" t="s">
+        <v>17</v>
+      </c>
+      <c r="G279">
+        <v>42</v>
+      </c>
+      <c r="H279">
+        <v>1</v>
+      </c>
+      <c r="I279">
+        <v>42</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279" s="2">
+        <v>1</v>
+      </c>
+      <c r="L279">
+        <v>42</v>
+      </c>
+      <c r="M279">
+        <v>0</v>
+      </c>
+      <c r="N279">
+        <v>0.96</v>
+      </c>
+      <c r="O279">
+        <v>0.20229166666666668</v>
+      </c>
+      <c r="P279" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>220</v>
+      </c>
+      <c r="B280" t="s">
+        <v>26</v>
+      </c>
+      <c r="C280">
+        <v>1442157</v>
+      </c>
+      <c r="D280" t="s">
+        <v>105</v>
+      </c>
+      <c r="E280" t="s">
+        <v>16</v>
+      </c>
+      <c r="F280" t="s">
+        <v>17</v>
+      </c>
+      <c r="G280">
+        <v>20</v>
+      </c>
+      <c r="H280">
+        <v>1</v>
+      </c>
+      <c r="I280">
+        <v>20</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280" s="2">
+        <v>1</v>
+      </c>
+      <c r="L280">
+        <v>20</v>
+      </c>
+      <c r="M280">
+        <v>0</v>
+      </c>
+      <c r="N280">
+        <v>1</v>
+      </c>
+      <c r="O280">
+        <v>0.10159722222222223</v>
+      </c>
+      <c r="P280" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>175</v>
+      </c>
+      <c r="B281" t="s">
+        <v>26</v>
+      </c>
+      <c r="C281">
+        <v>1399120</v>
+      </c>
+      <c r="D281" t="s">
+        <v>62</v>
+      </c>
+      <c r="E281" t="s">
+        <v>16</v>
+      </c>
+      <c r="F281" t="s">
+        <v>17</v>
+      </c>
+      <c r="G281">
+        <v>42</v>
+      </c>
+      <c r="H281">
+        <v>1</v>
+      </c>
+      <c r="I281">
+        <v>42</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281" s="2">
+        <v>1</v>
+      </c>
+      <c r="L281">
+        <v>42</v>
+      </c>
+      <c r="M281">
+        <v>0</v>
+      </c>
+      <c r="N281">
+        <v>0.94</v>
+      </c>
+      <c r="O281">
+        <v>0.23901620370370369</v>
+      </c>
+      <c r="P281" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>149</v>
+      </c>
+      <c r="B282" t="s">
+        <v>23</v>
+      </c>
+      <c r="C282">
+        <v>866660</v>
+      </c>
+      <c r="D282" t="s">
+        <v>36</v>
+      </c>
+      <c r="E282" t="s">
+        <v>16</v>
+      </c>
+      <c r="F282" t="s">
+        <v>17</v>
+      </c>
+      <c r="G282">
+        <v>48</v>
+      </c>
+      <c r="H282">
+        <v>1</v>
+      </c>
+      <c r="I282">
+        <v>48</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282" s="2">
+        <v>1</v>
+      </c>
+      <c r="L282">
+        <v>48</v>
+      </c>
+      <c r="M282">
+        <v>0</v>
+      </c>
+      <c r="N282">
+        <v>0.97</v>
+      </c>
+      <c r="O282">
+        <v>0.19418981481481482</v>
+      </c>
+      <c r="P282" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>164</v>
+      </c>
+      <c r="B283" t="s">
+        <v>30</v>
+      </c>
+      <c r="C283">
+        <v>1146887</v>
+      </c>
+      <c r="D283" t="s">
+        <v>51</v>
+      </c>
+      <c r="E283" t="s">
+        <v>16</v>
+      </c>
+      <c r="F283" t="s">
+        <v>17</v>
+      </c>
+      <c r="G283">
+        <v>76</v>
+      </c>
+      <c r="H283">
+        <v>1</v>
+      </c>
+      <c r="I283">
+        <v>76</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283" s="2">
+        <v>1</v>
+      </c>
+      <c r="L283">
+        <v>76</v>
+      </c>
+      <c r="M283">
+        <v>0</v>
+      </c>
+      <c r="N283">
+        <v>0.97</v>
+      </c>
+      <c r="O283">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="P283" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>235</v>
+      </c>
+      <c r="B284" t="s">
+        <v>19</v>
+      </c>
+      <c r="C284">
+        <v>1444023</v>
+      </c>
+      <c r="D284" t="s">
+        <v>119</v>
+      </c>
+      <c r="E284" t="s">
+        <v>16</v>
+      </c>
+      <c r="F284" t="s">
+        <v>17</v>
+      </c>
+      <c r="G284">
+        <v>16</v>
+      </c>
+      <c r="H284">
+        <v>1</v>
+      </c>
+      <c r="I284">
+        <v>16</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284" s="2">
+        <v>1</v>
+      </c>
+      <c r="L284">
+        <v>16</v>
+      </c>
+      <c r="M284">
+        <v>0</v>
+      </c>
+      <c r="N284">
+        <v>0.99</v>
+      </c>
+      <c r="O284">
+        <v>0.12815972222222222</v>
+      </c>
+      <c r="P284" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>135</v>
+      </c>
+      <c r="B285" t="s">
+        <v>19</v>
+      </c>
+      <c r="C285">
+        <v>843582</v>
+      </c>
+      <c r="D285" t="s">
+        <v>20</v>
+      </c>
+      <c r="E285" t="s">
+        <v>16</v>
+      </c>
+      <c r="F285" t="s">
+        <v>17</v>
+      </c>
+      <c r="G285">
+        <v>41</v>
+      </c>
+      <c r="H285">
+        <v>1</v>
+      </c>
+      <c r="I285">
+        <v>41</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285" s="2">
+        <v>1</v>
+      </c>
+      <c r="L285">
+        <v>41</v>
+      </c>
+      <c r="M285">
+        <v>0</v>
+      </c>
+      <c r="N285">
+        <v>0.97</v>
+      </c>
+      <c r="O285">
+        <v>0.46687499999999998</v>
+      </c>
+      <c r="P285" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>196</v>
+      </c>
+      <c r="B286" t="s">
+        <v>30</v>
+      </c>
+      <c r="C286">
+        <v>1424592</v>
+      </c>
+      <c r="D286" t="s">
+        <v>82</v>
+      </c>
+      <c r="E286" t="s">
+        <v>16</v>
+      </c>
+      <c r="F286" t="s">
+        <v>17</v>
+      </c>
+      <c r="G286">
+        <v>48</v>
+      </c>
+      <c r="H286">
+        <v>1</v>
+      </c>
+      <c r="I286">
+        <v>48</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286" s="2">
+        <v>1</v>
+      </c>
+      <c r="L286">
+        <v>48</v>
+      </c>
+      <c r="M286">
+        <v>0</v>
+      </c>
+      <c r="N286">
+        <v>0.95</v>
+      </c>
+      <c r="O286">
+        <v>0.46481481481481479</v>
+      </c>
+      <c r="P286" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>183</v>
+      </c>
+      <c r="B287" t="s">
+        <v>30</v>
+      </c>
+      <c r="C287">
+        <v>1409385</v>
+      </c>
+      <c r="D287" t="s">
+        <v>70</v>
+      </c>
+      <c r="E287" t="s">
+        <v>16</v>
+      </c>
+      <c r="F287" t="s">
+        <v>17</v>
+      </c>
+      <c r="G287">
+        <v>38</v>
+      </c>
+      <c r="H287">
+        <v>1</v>
+      </c>
+      <c r="I287">
+        <v>38</v>
+      </c>
+      <c r="J287">
+        <v>0</v>
+      </c>
+      <c r="K287" s="2">
+        <v>1</v>
+      </c>
+      <c r="L287">
+        <v>38</v>
+      </c>
+      <c r="M287">
+        <v>0</v>
+      </c>
+      <c r="N287">
+        <v>0.93</v>
+      </c>
+      <c r="O287">
+        <v>0.2020949074074074</v>
+      </c>
+      <c r="P287" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>246</v>
+      </c>
+      <c r="B288" t="s">
+        <v>26</v>
+      </c>
+      <c r="C288">
+        <v>1444346</v>
+      </c>
+      <c r="D288" t="s">
+        <v>129</v>
+      </c>
+      <c r="E288" t="s">
+        <v>16</v>
+      </c>
+      <c r="F288" t="s">
+        <v>17</v>
+      </c>
+      <c r="G288">
+        <v>19</v>
+      </c>
+      <c r="H288">
+        <v>1</v>
+      </c>
+      <c r="I288">
+        <v>19</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288" s="2">
+        <v>1</v>
+      </c>
+      <c r="L288">
+        <v>19</v>
+      </c>
+      <c r="M288">
+        <v>0</v>
+      </c>
+      <c r="N288">
+        <v>1</v>
+      </c>
+      <c r="O288">
+        <v>8.1666666666666665E-2</v>
+      </c>
+      <c r="P288" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>218</v>
+      </c>
+      <c r="B289" t="s">
+        <v>23</v>
+      </c>
+      <c r="C289">
+        <v>1442151</v>
+      </c>
+      <c r="D289" t="s">
+        <v>103</v>
+      </c>
+      <c r="E289" t="s">
+        <v>16</v>
+      </c>
+      <c r="F289" t="s">
+        <v>17</v>
+      </c>
+      <c r="G289">
+        <v>23</v>
+      </c>
+      <c r="H289">
+        <v>1</v>
+      </c>
+      <c r="I289">
+        <v>23</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289" s="2">
+        <v>1</v>
+      </c>
+      <c r="L289">
+        <v>23</v>
+      </c>
+      <c r="M289">
+        <v>0</v>
+      </c>
+      <c r="N289">
+        <v>0.99</v>
+      </c>
+      <c r="O289">
+        <v>0.1238425925925926</v>
+      </c>
+      <c r="P289" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>237</v>
+      </c>
+      <c r="B290" t="s">
+        <v>26</v>
+      </c>
+      <c r="C290">
+        <v>1444035</v>
+      </c>
+      <c r="D290" t="s">
+        <v>121</v>
+      </c>
+      <c r="E290" t="s">
+        <v>16</v>
+      </c>
+      <c r="F290" t="s">
+        <v>17</v>
+      </c>
+      <c r="G290">
+        <v>19</v>
+      </c>
+      <c r="H290">
+        <v>1</v>
+      </c>
+      <c r="I290">
+        <v>19</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290" s="2">
+        <v>1</v>
+      </c>
+      <c r="L290">
+        <v>19</v>
+      </c>
+      <c r="M290">
+        <v>0</v>
+      </c>
+      <c r="N290">
+        <v>0.94</v>
+      </c>
+      <c r="O290">
+        <v>0.16093749999999998</v>
+      </c>
+      <c r="P290" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>217</v>
+      </c>
+      <c r="B291" t="s">
+        <v>26</v>
+      </c>
+      <c r="C291">
+        <v>1442149</v>
+      </c>
+      <c r="D291" t="s">
+        <v>102</v>
+      </c>
+      <c r="E291" t="s">
+        <v>16</v>
+      </c>
+      <c r="F291" t="s">
+        <v>17</v>
+      </c>
+      <c r="G291">
+        <v>20</v>
+      </c>
+      <c r="H291">
+        <v>1</v>
+      </c>
+      <c r="I291">
+        <v>20</v>
+      </c>
+      <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291" s="2">
+        <v>1</v>
+      </c>
+      <c r="L291">
+        <v>20</v>
+      </c>
+      <c r="M291">
+        <v>0</v>
+      </c>
+      <c r="N291">
+        <v>0.98</v>
+      </c>
+      <c r="O291">
+        <v>7.3587962962962966E-2</v>
+      </c>
+      <c r="P291" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>158</v>
+      </c>
+      <c r="B292" t="s">
+        <v>30</v>
+      </c>
+      <c r="C292">
+        <v>1137214</v>
+      </c>
+      <c r="D292" t="s">
+        <v>45</v>
+      </c>
+      <c r="E292" t="s">
+        <v>16</v>
+      </c>
+      <c r="F292" t="s">
+        <v>17</v>
+      </c>
+      <c r="G292">
+        <v>62</v>
+      </c>
+      <c r="H292">
+        <v>1</v>
+      </c>
+      <c r="I292">
+        <v>62</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292" s="2">
+        <v>1</v>
+      </c>
+      <c r="L292">
+        <v>62</v>
+      </c>
+      <c r="M292">
+        <v>0</v>
+      </c>
+      <c r="N292">
+        <v>0.97</v>
+      </c>
+      <c r="O292">
+        <v>0.41085648148148146</v>
+      </c>
+      <c r="P292" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>165</v>
+      </c>
+      <c r="B293" t="s">
+        <v>26</v>
+      </c>
+      <c r="C293">
+        <v>1146908</v>
+      </c>
+      <c r="D293" t="s">
+        <v>52</v>
+      </c>
+      <c r="E293" t="s">
+        <v>16</v>
+      </c>
+      <c r="F293" t="s">
+        <v>17</v>
+      </c>
+      <c r="G293">
+        <v>62</v>
+      </c>
+      <c r="H293">
+        <v>1</v>
+      </c>
+      <c r="I293">
+        <v>62</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293" s="2">
+        <v>1</v>
+      </c>
+      <c r="L293">
+        <v>62</v>
+      </c>
+      <c r="M293">
+        <v>0</v>
+      </c>
+      <c r="N293">
+        <v>0.96</v>
+      </c>
+      <c r="O293">
+        <v>0.27952546296296293</v>
+      </c>
+      <c r="P293" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>232</v>
+      </c>
+      <c r="B294" t="s">
+        <v>23</v>
+      </c>
+      <c r="C294">
+        <v>1443734</v>
+      </c>
+      <c r="D294" t="s">
+        <v>117</v>
+      </c>
+      <c r="E294" t="s">
+        <v>16</v>
+      </c>
+      <c r="F294" t="s">
+        <v>17</v>
+      </c>
+      <c r="G294">
+        <v>22</v>
+      </c>
+      <c r="H294">
+        <v>1</v>
+      </c>
+      <c r="I294">
+        <v>22</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294" s="2">
+        <v>1</v>
+      </c>
+      <c r="L294">
+        <v>22</v>
+      </c>
+      <c r="M294">
+        <v>0</v>
+      </c>
+      <c r="N294">
+        <v>0.99</v>
+      </c>
+      <c r="O294">
+        <v>8.3252314814814821E-2</v>
+      </c>
+      <c r="P294" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>204</v>
+      </c>
+      <c r="B295" t="s">
+        <v>26</v>
+      </c>
+      <c r="C295">
+        <v>1430177</v>
+      </c>
+      <c r="D295" t="s">
+        <v>89</v>
+      </c>
+      <c r="E295" t="s">
+        <v>16</v>
+      </c>
+      <c r="F295" t="s">
+        <v>17</v>
+      </c>
+      <c r="G295">
+        <v>29</v>
+      </c>
+      <c r="H295">
+        <v>1</v>
+      </c>
+      <c r="I295">
+        <v>29</v>
+      </c>
+      <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295" s="2">
+        <v>1</v>
+      </c>
+      <c r="L295">
+        <v>29</v>
+      </c>
+      <c r="M295">
+        <v>0</v>
+      </c>
+      <c r="N295">
+        <v>0.91</v>
+      </c>
+      <c r="O295">
+        <v>0.15010416666666668</v>
+      </c>
+      <c r="P295" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>156</v>
+      </c>
+      <c r="B296" t="s">
+        <v>26</v>
+      </c>
+      <c r="C296">
+        <v>1113329</v>
+      </c>
+      <c r="D296" t="s">
+        <v>43</v>
+      </c>
+      <c r="E296" t="s">
+        <v>16</v>
+      </c>
+      <c r="F296" t="s">
+        <v>17</v>
+      </c>
+      <c r="G296">
+        <v>41</v>
+      </c>
+      <c r="H296">
+        <v>1</v>
+      </c>
+      <c r="I296">
+        <v>41</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296" s="2">
+        <v>1</v>
+      </c>
+      <c r="L296">
+        <v>41</v>
+      </c>
+      <c r="M296">
+        <v>0</v>
+      </c>
+      <c r="N296">
+        <v>0.96</v>
+      </c>
+      <c r="O296">
+        <v>0.21256944444444445</v>
+      </c>
+      <c r="P296" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>210</v>
+      </c>
+      <c r="B297" t="s">
+        <v>23</v>
+      </c>
+      <c r="C297">
+        <v>1440375</v>
+      </c>
+      <c r="D297" t="s">
+        <v>95</v>
+      </c>
+      <c r="E297" t="s">
+        <v>16</v>
+      </c>
+      <c r="F297" t="s">
+        <v>17</v>
+      </c>
+      <c r="G297">
+        <v>29</v>
+      </c>
+      <c r="H297">
+        <v>1</v>
+      </c>
+      <c r="I297">
+        <v>29</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297" s="2">
+        <v>1</v>
+      </c>
+      <c r="L297">
+        <v>29</v>
+      </c>
+      <c r="M297">
+        <v>0</v>
+      </c>
+      <c r="N297">
+        <v>0.94</v>
+      </c>
+      <c r="O297">
+        <v>0.15065972222222221</v>
+      </c>
+      <c r="P297" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>174</v>
+      </c>
+      <c r="B298" t="s">
+        <v>23</v>
+      </c>
+      <c r="C298">
+        <v>1396914</v>
+      </c>
+      <c r="D298" t="s">
+        <v>61</v>
+      </c>
+      <c r="E298" t="s">
+        <v>16</v>
+      </c>
+      <c r="F298" t="s">
+        <v>17</v>
+      </c>
+      <c r="G298">
+        <v>62</v>
+      </c>
+      <c r="H298">
+        <v>1</v>
+      </c>
+      <c r="I298">
+        <v>62</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298" s="2">
+        <v>1</v>
+      </c>
+      <c r="L298">
+        <v>62</v>
+      </c>
+      <c r="M298">
+        <v>0</v>
+      </c>
+      <c r="N298">
+        <v>0.95</v>
+      </c>
+      <c r="O298">
+        <v>0.23619212962962963</v>
+      </c>
+      <c r="P298" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>268</v>
+      </c>
+      <c r="B299" t="s">
+        <v>30</v>
+      </c>
+      <c r="C299">
+        <v>1104316</v>
+      </c>
+      <c r="D299" t="s">
+        <v>255</v>
+      </c>
+      <c r="E299" t="s">
+        <v>16</v>
+      </c>
+      <c r="F299" t="s">
+        <v>17</v>
+      </c>
+      <c r="G299">
+        <v>62</v>
+      </c>
+      <c r="H299">
+        <v>1</v>
+      </c>
+      <c r="I299">
+        <v>62</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299" s="2">
+        <v>1</v>
+      </c>
+      <c r="L299">
+        <v>62</v>
+      </c>
+      <c r="M299">
+        <v>0</v>
+      </c>
+      <c r="N299">
+        <v>0.97</v>
+      </c>
+      <c r="O299">
+        <v>0.30690972222222224</v>
+      </c>
+      <c r="P299" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>202</v>
+      </c>
+      <c r="B300" t="s">
+        <v>30</v>
+      </c>
+      <c r="C300">
+        <v>1429086</v>
+      </c>
+      <c r="D300" t="s">
+        <v>87</v>
+      </c>
+      <c r="E300" t="s">
+        <v>16</v>
+      </c>
+      <c r="F300" t="s">
+        <v>17</v>
+      </c>
+      <c r="G300">
+        <v>32</v>
+      </c>
+      <c r="H300">
+        <v>1</v>
+      </c>
+      <c r="I300">
+        <v>32</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300" s="2">
+        <v>1</v>
+      </c>
+      <c r="L300">
+        <v>32</v>
+      </c>
+      <c r="M300">
+        <v>0</v>
+      </c>
+      <c r="N300">
+        <v>0.97</v>
+      </c>
+      <c r="O300">
+        <v>0.14609953703703704</v>
+      </c>
+      <c r="P300" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>230</v>
+      </c>
+      <c r="B301" t="s">
+        <v>26</v>
+      </c>
+      <c r="C301">
+        <v>1442515</v>
+      </c>
+      <c r="D301" t="s">
+        <v>115</v>
+      </c>
+      <c r="E301" t="s">
+        <v>16</v>
+      </c>
+      <c r="F301" t="s">
+        <v>17</v>
+      </c>
+      <c r="G301">
+        <v>20</v>
+      </c>
+      <c r="H301">
+        <v>0.95</v>
+      </c>
+      <c r="I301">
+        <v>19</v>
+      </c>
+      <c r="J301">
+        <v>1</v>
+      </c>
+      <c r="K301" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L301">
+        <v>19</v>
+      </c>
+      <c r="M301">
+        <v>0</v>
+      </c>
+      <c r="N301">
+        <v>1</v>
+      </c>
+      <c r="O301">
+        <v>9.2500000000000013E-2</v>
+      </c>
+      <c r="P301" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>162</v>
+      </c>
+      <c r="B302" t="s">
+        <v>19</v>
+      </c>
+      <c r="C302">
+        <v>1145964</v>
+      </c>
+      <c r="D302" t="s">
+        <v>49</v>
+      </c>
+      <c r="E302" t="s">
+        <v>16</v>
+      </c>
+      <c r="F302" t="s">
+        <v>17</v>
+      </c>
+      <c r="G302">
+        <v>23</v>
+      </c>
+      <c r="H302">
+        <v>0.96</v>
+      </c>
+      <c r="I302">
+        <v>22</v>
+      </c>
+      <c r="J302">
+        <v>1</v>
+      </c>
+      <c r="K302" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="L302">
+        <v>22</v>
+      </c>
+      <c r="M302">
+        <v>0</v>
+      </c>
+      <c r="N302">
+        <v>0.88</v>
+      </c>
+      <c r="O302">
+        <v>0.22033564814814813</v>
+      </c>
+      <c r="P302" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>226</v>
+      </c>
+      <c r="B303" t="s">
+        <v>26</v>
+      </c>
+      <c r="C303">
+        <v>1442336</v>
+      </c>
+      <c r="D303" t="s">
+        <v>111</v>
+      </c>
+      <c r="E303" t="s">
+        <v>16</v>
+      </c>
+      <c r="F303" t="s">
+        <v>17</v>
+      </c>
+      <c r="G303">
+        <v>21</v>
+      </c>
+      <c r="H303">
+        <v>0.95</v>
+      </c>
+      <c r="I303">
+        <v>20</v>
+      </c>
+      <c r="J303">
+        <v>1</v>
+      </c>
+      <c r="K303" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L303">
+        <v>20</v>
+      </c>
+      <c r="M303">
+        <v>0</v>
+      </c>
+      <c r="N303">
+        <v>0.99</v>
+      </c>
+      <c r="O303">
+        <v>9.7025462962962952E-2</v>
+      </c>
+      <c r="P303" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>187</v>
+      </c>
+      <c r="B304" t="s">
+        <v>26</v>
+      </c>
+      <c r="C304">
+        <v>1412115</v>
+      </c>
+      <c r="D304" t="s">
+        <v>73</v>
+      </c>
+      <c r="E304" t="s">
+        <v>16</v>
+      </c>
+      <c r="F304" t="s">
+        <v>17</v>
+      </c>
+      <c r="G304">
+        <v>47</v>
+      </c>
+      <c r="H304">
+        <v>1</v>
+      </c>
+      <c r="I304">
+        <v>47</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304" s="2">
+        <v>1</v>
+      </c>
+      <c r="L304">
+        <v>47</v>
+      </c>
+      <c r="M304">
+        <v>0</v>
+      </c>
+      <c r="N304">
+        <v>0.95</v>
+      </c>
+      <c r="O304">
+        <v>0.21596064814814817</v>
+      </c>
+      <c r="P304" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>145</v>
+      </c>
+      <c r="B305" t="s">
+        <v>133</v>
+      </c>
+      <c r="C305">
+        <v>863224</v>
+      </c>
+      <c r="D305" t="s">
+        <v>32</v>
+      </c>
+      <c r="E305" t="s">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>17</v>
+      </c>
+      <c r="G305">
+        <v>52</v>
+      </c>
+      <c r="H305">
+        <v>0.96</v>
+      </c>
+      <c r="I305">
+        <v>50</v>
+      </c>
+      <c r="J305">
+        <v>2</v>
+      </c>
+      <c r="K305" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="L305">
+        <v>50</v>
+      </c>
+      <c r="M305">
+        <v>0</v>
+      </c>
+      <c r="N305">
+        <v>0.94</v>
+      </c>
+      <c r="O305">
+        <v>0.6007986111111111</v>
+      </c>
+      <c r="P305" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="306" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>238</v>
+      </c>
+      <c r="B306" t="s">
+        <v>26</v>
+      </c>
+      <c r="C306">
+        <v>1444167</v>
+      </c>
+      <c r="D306" t="s">
+        <v>122</v>
+      </c>
+      <c r="E306" t="s">
+        <v>16</v>
+      </c>
+      <c r="F306" t="s">
+        <v>17</v>
+      </c>
+      <c r="G306">
+        <v>22</v>
+      </c>
+      <c r="H306">
+        <v>1</v>
+      </c>
+      <c r="I306">
+        <v>22</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306" s="2">
+        <v>1</v>
+      </c>
+      <c r="L306">
+        <v>22</v>
+      </c>
+      <c r="M306">
+        <v>0</v>
+      </c>
+      <c r="N306">
+        <v>0.95</v>
+      </c>
+      <c r="O306">
+        <v>0.14659722222222224</v>
+      </c>
+      <c r="P306" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="307" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>208</v>
+      </c>
+      <c r="B307" t="s">
+        <v>26</v>
+      </c>
+      <c r="C307">
+        <v>1440103</v>
+      </c>
+      <c r="D307" t="s">
+        <v>93</v>
+      </c>
+      <c r="E307" t="s">
+        <v>16</v>
+      </c>
+      <c r="F307" t="s">
+        <v>17</v>
+      </c>
+      <c r="G307">
+        <v>32</v>
+      </c>
+      <c r="H307">
+        <v>1</v>
+      </c>
+      <c r="I307">
+        <v>32</v>
+      </c>
+      <c r="J307">
+        <v>0</v>
+      </c>
+      <c r="K307" s="2">
+        <v>1</v>
+      </c>
+      <c r="L307">
+        <v>32</v>
+      </c>
+      <c r="M307">
+        <v>0</v>
+      </c>
+      <c r="N307">
+        <v>0.95</v>
+      </c>
+      <c r="O307">
+        <v>0.18096064814814816</v>
+      </c>
+      <c r="P307" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="308" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>212</v>
+      </c>
+      <c r="B308" t="s">
+        <v>30</v>
+      </c>
+      <c r="C308">
+        <v>1440643</v>
+      </c>
+      <c r="D308" t="s">
+        <v>97</v>
+      </c>
+      <c r="E308" t="s">
+        <v>16</v>
+      </c>
+      <c r="F308" t="s">
+        <v>17</v>
+      </c>
+      <c r="G308">
+        <v>22</v>
+      </c>
+      <c r="H308">
+        <v>1</v>
+      </c>
+      <c r="I308">
+        <v>22</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308" s="2">
+        <v>1</v>
+      </c>
+      <c r="L308">
+        <v>22</v>
+      </c>
+      <c r="M308">
+        <v>0</v>
+      </c>
+      <c r="N308">
+        <v>0.99</v>
+      </c>
+      <c r="O308">
+        <v>9.8449074074074064E-2</v>
+      </c>
+      <c r="P308" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="309" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>239</v>
+      </c>
+      <c r="B309" t="s">
+        <v>26</v>
+      </c>
+      <c r="C309">
+        <v>1444304</v>
+      </c>
+      <c r="D309" t="s">
+        <v>123</v>
+      </c>
+      <c r="E309" t="s">
+        <v>16</v>
+      </c>
+      <c r="F309" t="s">
+        <v>17</v>
+      </c>
+      <c r="G309">
+        <v>19</v>
+      </c>
+      <c r="H309">
+        <v>1</v>
+      </c>
+      <c r="I309">
+        <v>19</v>
+      </c>
+      <c r="J309">
+        <v>0</v>
+      </c>
+      <c r="K309" s="2">
+        <v>1</v>
+      </c>
+      <c r="L309">
+        <v>19</v>
+      </c>
+      <c r="M309">
+        <v>0</v>
+      </c>
+      <c r="N309">
+        <v>0.98</v>
+      </c>
+      <c r="O309">
+        <v>7.6053240740740741E-2</v>
+      </c>
+      <c r="P309" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="310" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>169</v>
+      </c>
+      <c r="B310" t="s">
+        <v>30</v>
+      </c>
+      <c r="C310">
+        <v>1150507</v>
+      </c>
+      <c r="D310" t="s">
+        <v>56</v>
+      </c>
+      <c r="E310" t="s">
+        <v>16</v>
+      </c>
+      <c r="F310" t="s">
+        <v>17</v>
+      </c>
+      <c r="G310">
+        <v>62</v>
+      </c>
+      <c r="H310">
+        <v>1</v>
+      </c>
+      <c r="I310">
+        <v>62</v>
+      </c>
+      <c r="J310">
+        <v>0</v>
+      </c>
+      <c r="K310" s="2">
+        <v>1</v>
+      </c>
+      <c r="L310">
+        <v>62</v>
+      </c>
+      <c r="M310">
+        <v>0</v>
+      </c>
+      <c r="N310">
+        <v>0.98</v>
+      </c>
+      <c r="O310">
+        <v>0.2421875</v>
+      </c>
+      <c r="P310" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="311" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>166</v>
+      </c>
+      <c r="B311" t="s">
+        <v>30</v>
+      </c>
+      <c r="C311">
+        <v>1146910</v>
+      </c>
+      <c r="D311" t="s">
+        <v>53</v>
+      </c>
+      <c r="E311" t="s">
+        <v>16</v>
+      </c>
+      <c r="F311" t="s">
+        <v>17</v>
+      </c>
+      <c r="G311">
+        <v>62</v>
+      </c>
+      <c r="H311">
+        <v>1</v>
+      </c>
+      <c r="I311">
+        <v>62</v>
+      </c>
+      <c r="J311">
+        <v>0</v>
+      </c>
+      <c r="K311" s="2">
+        <v>1</v>
+      </c>
+      <c r="L311">
+        <v>62</v>
+      </c>
+      <c r="M311">
+        <v>0</v>
+      </c>
+      <c r="N311">
+        <v>0.96</v>
+      </c>
+      <c r="O311">
+        <v>0.3536111111111111</v>
+      </c>
+      <c r="P311" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="312" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>170</v>
+      </c>
+      <c r="B312" t="s">
+        <v>26</v>
+      </c>
+      <c r="C312">
+        <v>1152265</v>
+      </c>
+      <c r="D312" t="s">
+        <v>57</v>
+      </c>
+      <c r="E312" t="s">
+        <v>16</v>
+      </c>
+      <c r="F312" t="s">
+        <v>17</v>
+      </c>
+      <c r="G312">
+        <v>62</v>
+      </c>
+      <c r="H312">
+        <v>1</v>
+      </c>
+      <c r="I312">
+        <v>62</v>
+      </c>
+      <c r="J312">
+        <v>0</v>
+      </c>
+      <c r="K312" s="2">
+        <v>1</v>
+      </c>
+      <c r="L312">
+        <v>62</v>
+      </c>
+      <c r="M312">
+        <v>0</v>
+      </c>
+      <c r="N312">
+        <v>0.97</v>
+      </c>
+      <c r="O312">
+        <v>0.40586805555555555</v>
+      </c>
+      <c r="P312" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="313" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>150</v>
+      </c>
+      <c r="B313" t="s">
+        <v>26</v>
+      </c>
+      <c r="C313">
+        <v>866699</v>
+      </c>
+      <c r="D313" t="s">
+        <v>37</v>
+      </c>
+      <c r="E313" t="s">
+        <v>16</v>
+      </c>
+      <c r="F313" t="s">
+        <v>17</v>
+      </c>
+      <c r="G313">
+        <v>62</v>
+      </c>
+      <c r="H313">
+        <v>1</v>
+      </c>
+      <c r="I313">
+        <v>62</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313" s="2">
+        <v>1</v>
+      </c>
+      <c r="L313">
+        <v>62</v>
+      </c>
+      <c r="M313">
+        <v>0</v>
+      </c>
+      <c r="N313">
+        <v>0.95</v>
+      </c>
+      <c r="O313">
+        <v>0.42883101851851851</v>
+      </c>
+      <c r="P313" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="314" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>141</v>
+      </c>
+      <c r="B314" t="s">
+        <v>19</v>
+      </c>
+      <c r="C314">
+        <v>860177</v>
+      </c>
+      <c r="D314" t="s">
+        <v>28</v>
+      </c>
+      <c r="E314" t="s">
+        <v>16</v>
+      </c>
+      <c r="F314" t="s">
+        <v>17</v>
+      </c>
+      <c r="G314">
+        <v>46</v>
+      </c>
+      <c r="H314">
+        <v>1</v>
+      </c>
+      <c r="I314">
+        <v>46</v>
+      </c>
+      <c r="J314">
+        <v>0</v>
+      </c>
+      <c r="K314" s="2">
+        <v>1</v>
+      </c>
+      <c r="L314">
+        <v>46</v>
+      </c>
+      <c r="M314">
+        <v>0</v>
+      </c>
+      <c r="N314">
+        <v>0.92</v>
+      </c>
+      <c r="O314">
+        <v>0.45887731481481481</v>
+      </c>
+      <c r="P314" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="315" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>185</v>
+      </c>
+      <c r="B315" t="s">
+        <v>26</v>
+      </c>
+      <c r="C315">
+        <v>1411494</v>
+      </c>
+      <c r="D315" t="s">
+        <v>28</v>
+      </c>
+      <c r="E315" t="s">
+        <v>16</v>
+      </c>
+      <c r="F315" t="s">
+        <v>17</v>
+      </c>
+      <c r="G315">
+        <v>48</v>
+      </c>
+      <c r="H315">
+        <v>1</v>
+      </c>
+      <c r="I315">
+        <v>48</v>
+      </c>
+      <c r="J315">
+        <v>0</v>
+      </c>
+      <c r="K315" s="2">
+        <v>1</v>
+      </c>
+      <c r="L315">
+        <v>48</v>
+      </c>
+      <c r="M315">
+        <v>0</v>
+      </c>
+      <c r="N315">
+        <v>0.9</v>
+      </c>
+      <c r="O315">
+        <v>0.25518518518518518</v>
+      </c>
+      <c r="P315" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="316" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>243</v>
+      </c>
+      <c r="B316" t="s">
+        <v>30</v>
+      </c>
+      <c r="C316">
+        <v>1444313</v>
+      </c>
+      <c r="D316" t="s">
+        <v>126</v>
+      </c>
+      <c r="E316" t="s">
+        <v>16</v>
+      </c>
+      <c r="F316" t="s">
+        <v>17</v>
+      </c>
+      <c r="G316">
+        <v>19</v>
+      </c>
+      <c r="H316">
+        <v>1</v>
+      </c>
+      <c r="I316">
+        <v>19</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316" s="2">
+        <v>1</v>
+      </c>
+      <c r="L316">
+        <v>19</v>
+      </c>
+      <c r="M316">
+        <v>0</v>
+      </c>
+      <c r="N316">
+        <v>0.97</v>
+      </c>
+      <c r="O316">
+        <v>0.13202546296296297</v>
+      </c>
+      <c r="P316" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="317" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>207</v>
+      </c>
+      <c r="B317" t="s">
+        <v>23</v>
+      </c>
+      <c r="C317">
+        <v>1440100</v>
+      </c>
+      <c r="D317" t="s">
+        <v>92</v>
+      </c>
+      <c r="E317" t="s">
+        <v>16</v>
+      </c>
+      <c r="F317" t="s">
+        <v>17</v>
+      </c>
+      <c r="G317">
+        <v>32</v>
+      </c>
+      <c r="H317">
+        <v>1</v>
+      </c>
+      <c r="I317">
+        <v>32</v>
+      </c>
+      <c r="J317">
+        <v>0</v>
+      </c>
+      <c r="K317" s="2">
+        <v>1</v>
+      </c>
+      <c r="L317">
+        <v>32</v>
+      </c>
+      <c r="M317">
+        <v>0</v>
+      </c>
+      <c r="N317">
+        <v>0.89</v>
+      </c>
+      <c r="O317">
+        <v>0.14218749999999999</v>
+      </c>
+      <c r="P317" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="318" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>186</v>
+      </c>
+      <c r="B318" t="s">
+        <v>26</v>
+      </c>
+      <c r="C318">
+        <v>1412087</v>
+      </c>
+      <c r="D318" t="s">
+        <v>72</v>
+      </c>
+      <c r="E318" t="s">
+        <v>16</v>
+      </c>
+      <c r="F318" t="s">
+        <v>17</v>
+      </c>
+      <c r="G318">
+        <v>57</v>
+      </c>
+      <c r="H318">
+        <v>0.98</v>
+      </c>
+      <c r="I318">
+        <v>56</v>
+      </c>
+      <c r="J318">
+        <v>1</v>
+      </c>
+      <c r="K318" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="L318">
+        <v>56</v>
+      </c>
+      <c r="M318">
+        <v>0</v>
+      </c>
+      <c r="N318">
+        <v>0.97</v>
+      </c>
+      <c r="O318">
+        <v>0.23869212962962963</v>
+      </c>
+      <c r="P318" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="319" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>181</v>
+      </c>
+      <c r="B319" t="s">
+        <v>30</v>
+      </c>
+      <c r="C319">
+        <v>1407180</v>
+      </c>
+      <c r="D319" t="s">
+        <v>68</v>
+      </c>
+      <c r="E319" t="s">
+        <v>16</v>
+      </c>
+      <c r="F319" t="s">
+        <v>17</v>
+      </c>
+      <c r="G319">
+        <v>49</v>
+      </c>
+      <c r="H319">
+        <v>1</v>
+      </c>
+      <c r="I319">
+        <v>49</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319" s="2">
+        <v>1</v>
+      </c>
+      <c r="L319">
+        <v>49</v>
+      </c>
+      <c r="M319">
+        <v>0</v>
+      </c>
+      <c r="N319">
+        <v>0.94</v>
+      </c>
+      <c r="O319">
+        <v>0.22318287037037035</v>
+      </c>
+      <c r="P319" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="320" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>189</v>
+      </c>
+      <c r="B320" t="s">
+        <v>23</v>
+      </c>
+      <c r="C320">
+        <v>1412891</v>
+      </c>
+      <c r="D320" t="s">
+        <v>75</v>
+      </c>
+      <c r="E320" t="s">
+        <v>16</v>
+      </c>
+      <c r="F320" t="s">
+        <v>17</v>
+      </c>
+      <c r="G320">
+        <v>50</v>
+      </c>
+      <c r="H320">
+        <v>1</v>
+      </c>
+      <c r="I320">
+        <v>50</v>
+      </c>
+      <c r="J320">
+        <v>0</v>
+      </c>
+      <c r="K320" s="2">
+        <v>1</v>
+      </c>
+      <c r="L320">
+        <v>50</v>
+      </c>
+      <c r="M320">
+        <v>0</v>
+      </c>
+      <c r="N320">
+        <v>0.93</v>
+      </c>
+      <c r="O320">
+        <v>0.24653935185185186</v>
+      </c>
+      <c r="P320" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="321" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>167</v>
+      </c>
+      <c r="B321" t="s">
+        <v>30</v>
+      </c>
+      <c r="C321">
+        <v>1148415</v>
+      </c>
+      <c r="D321" t="s">
+        <v>54</v>
+      </c>
+      <c r="E321" t="s">
+        <v>16</v>
+      </c>
+      <c r="F321" t="s">
+        <v>17</v>
+      </c>
+      <c r="G321">
+        <v>42</v>
+      </c>
+      <c r="H321">
+        <v>1</v>
+      </c>
+      <c r="I321">
+        <v>42</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+      <c r="K321" s="2">
+        <v>1</v>
+      </c>
+      <c r="L321">
+        <v>42</v>
+      </c>
+      <c r="M321">
+        <v>0</v>
+      </c>
+      <c r="N321">
+        <v>0.96</v>
+      </c>
+      <c r="O321">
+        <v>0.20363425925925926</v>
+      </c>
+      <c r="P321" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="322" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>211</v>
+      </c>
+      <c r="B322" t="s">
+        <v>30</v>
+      </c>
+      <c r="C322">
+        <v>1440637</v>
+      </c>
+      <c r="D322" t="s">
+        <v>96</v>
+      </c>
+      <c r="E322" t="s">
+        <v>16</v>
+      </c>
+      <c r="F322" t="s">
+        <v>17</v>
+      </c>
+      <c r="G322">
+        <v>22</v>
+      </c>
+      <c r="H322">
+        <v>1</v>
+      </c>
+      <c r="I322">
+        <v>22</v>
+      </c>
+      <c r="J322">
+        <v>0</v>
+      </c>
+      <c r="K322" s="2">
+        <v>1</v>
+      </c>
+      <c r="L322">
+        <v>22</v>
+      </c>
+      <c r="M322">
+        <v>0</v>
+      </c>
+      <c r="N322">
+        <v>0.91</v>
+      </c>
+      <c r="O322">
+        <v>0.14708333333333334</v>
+      </c>
+      <c r="P322" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="323" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>190</v>
+      </c>
+      <c r="B323" t="s">
+        <v>23</v>
+      </c>
+      <c r="C323">
+        <v>1414124</v>
+      </c>
+      <c r="D323" t="s">
+        <v>76</v>
+      </c>
+      <c r="E323" t="s">
+        <v>16</v>
+      </c>
+      <c r="F323" t="s">
+        <v>17</v>
+      </c>
+      <c r="G323">
+        <v>41</v>
+      </c>
+      <c r="H323">
+        <v>1</v>
+      </c>
+      <c r="I323">
+        <v>41</v>
+      </c>
+      <c r="J323">
+        <v>0</v>
+      </c>
+      <c r="K323" s="2">
+        <v>1</v>
+      </c>
+      <c r="L323">
+        <v>41</v>
+      </c>
+      <c r="M323">
+        <v>0</v>
+      </c>
+      <c r="N323">
+        <v>0.98</v>
+      </c>
+      <c r="O323">
+        <v>0.22679398148148147</v>
+      </c>
+      <c r="P323" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="324" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>205</v>
+      </c>
+      <c r="B324" t="s">
+        <v>26</v>
+      </c>
+      <c r="C324">
+        <v>1430805</v>
+      </c>
+      <c r="D324" t="s">
+        <v>90</v>
+      </c>
+      <c r="E324" t="s">
+        <v>16</v>
+      </c>
+      <c r="F324" t="s">
+        <v>17</v>
+      </c>
+      <c r="G324">
+        <v>29</v>
+      </c>
+      <c r="H324">
+        <v>1</v>
+      </c>
+      <c r="I324">
+        <v>29</v>
+      </c>
+      <c r="J324">
+        <v>0</v>
+      </c>
+      <c r="K324" s="2">
+        <v>1</v>
+      </c>
+      <c r="L324">
+        <v>29</v>
+      </c>
+      <c r="M324">
+        <v>0</v>
+      </c>
+      <c r="N324">
+        <v>0.95</v>
+      </c>
+      <c r="O324">
+        <v>0.14381944444444444</v>
+      </c>
+      <c r="P324" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="325" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>201</v>
+      </c>
+      <c r="B325" t="s">
+        <v>19</v>
+      </c>
+      <c r="C325">
+        <v>1428338</v>
+      </c>
+      <c r="D325" t="s">
+        <v>86</v>
+      </c>
+      <c r="E325" t="s">
+        <v>16</v>
+      </c>
+      <c r="F325" t="s">
+        <v>17</v>
+      </c>
+      <c r="G325">
+        <v>23</v>
+      </c>
+      <c r="H325">
+        <v>1</v>
+      </c>
+      <c r="I325">
+        <v>23</v>
+      </c>
+      <c r="J325">
+        <v>0</v>
+      </c>
+      <c r="K325" s="2">
+        <v>1</v>
+      </c>
+      <c r="L325">
+        <v>23</v>
+      </c>
+      <c r="M325">
+        <v>0</v>
+      </c>
+      <c r="N325">
+        <v>0.95</v>
+      </c>
+      <c r="O325">
+        <v>0.13238425925925926</v>
+      </c>
+      <c r="P325" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="326" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>134</v>
+      </c>
+      <c r="B326" t="s">
+        <v>30</v>
+      </c>
+      <c r="C326">
+        <v>843117</v>
+      </c>
+      <c r="D326" t="s">
+        <v>18</v>
+      </c>
+      <c r="E326" t="s">
+        <v>16</v>
+      </c>
+      <c r="F326" t="s">
+        <v>17</v>
+      </c>
+      <c r="G326">
+        <v>89</v>
+      </c>
+      <c r="H326">
+        <v>0.99</v>
+      </c>
+      <c r="I326">
+        <v>88</v>
+      </c>
+      <c r="J326">
+        <v>1</v>
+      </c>
+      <c r="K326" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="L326">
+        <v>88</v>
+      </c>
+      <c r="M326">
+        <v>0</v>
+      </c>
+      <c r="N326">
+        <v>0.96</v>
+      </c>
+      <c r="O326">
+        <v>0.57467592592592587</v>
+      </c>
+      <c r="P326" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="327" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>188</v>
+      </c>
+      <c r="B327" t="s">
+        <v>30</v>
+      </c>
+      <c r="C327">
+        <v>1412869</v>
+      </c>
+      <c r="D327" t="s">
+        <v>74</v>
+      </c>
+      <c r="E327" t="s">
+        <v>16</v>
+      </c>
+      <c r="F327" t="s">
+        <v>17</v>
+      </c>
+      <c r="G327">
+        <v>56</v>
+      </c>
+      <c r="H327">
+        <v>1</v>
+      </c>
+      <c r="I327">
+        <v>56</v>
+      </c>
+      <c r="J327">
+        <v>0</v>
+      </c>
+      <c r="K327" s="2">
+        <v>1</v>
+      </c>
+      <c r="L327">
+        <v>56</v>
+      </c>
+      <c r="M327">
+        <v>0</v>
+      </c>
+      <c r="N327">
+        <v>0.93</v>
+      </c>
+      <c r="O327">
+        <v>0.22116898148148148</v>
+      </c>
+      <c r="P327" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="328" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>140</v>
+      </c>
+      <c r="B328" t="s">
+        <v>26</v>
+      </c>
+      <c r="C328">
+        <v>858933</v>
+      </c>
+      <c r="D328" t="s">
+        <v>27</v>
+      </c>
+      <c r="E328" t="s">
+        <v>16</v>
+      </c>
+      <c r="F328" t="s">
+        <v>17</v>
+      </c>
+      <c r="G328">
+        <v>32</v>
+      </c>
+      <c r="H328">
+        <v>1</v>
+      </c>
+      <c r="I328">
+        <v>32</v>
+      </c>
+      <c r="J328">
+        <v>0</v>
+      </c>
+      <c r="K328" s="2">
+        <v>1</v>
+      </c>
+      <c r="L328">
+        <v>32</v>
+      </c>
+      <c r="M328">
+        <v>0</v>
+      </c>
+      <c r="N328">
+        <v>0.98</v>
+      </c>
+      <c r="O328">
+        <v>0.13468749999999999</v>
+      </c>
+      <c r="P328" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="329" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>215</v>
+      </c>
+      <c r="B329" t="s">
+        <v>26</v>
+      </c>
+      <c r="C329">
+        <v>1442140</v>
+      </c>
+      <c r="D329" t="s">
+        <v>100</v>
+      </c>
+      <c r="E329" t="s">
+        <v>16</v>
+      </c>
+      <c r="F329" t="s">
+        <v>17</v>
+      </c>
+      <c r="G329">
+        <v>23</v>
+      </c>
+      <c r="H329">
+        <v>0.96</v>
+      </c>
+      <c r="I329">
+        <v>22</v>
+      </c>
+      <c r="J329">
+        <v>1</v>
+      </c>
+      <c r="K329" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="L329">
+        <v>22</v>
+      </c>
+      <c r="M329">
+        <v>0</v>
+      </c>
+      <c r="N329">
+        <v>0.97</v>
+      </c>
+      <c r="O329">
+        <v>0.59692129629629631</v>
+      </c>
+      <c r="P329" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="330" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>225</v>
+      </c>
+      <c r="B330" t="s">
+        <v>30</v>
+      </c>
+      <c r="C330">
+        <v>1442198</v>
+      </c>
+      <c r="D330" t="s">
+        <v>110</v>
+      </c>
+      <c r="E330" t="s">
+        <v>16</v>
+      </c>
+      <c r="F330" t="s">
+        <v>17</v>
+      </c>
+      <c r="G330">
+        <v>23</v>
+      </c>
+      <c r="H330">
+        <v>0.96</v>
+      </c>
+      <c r="I330">
+        <v>22</v>
+      </c>
+      <c r="J330">
+        <v>1</v>
+      </c>
+      <c r="K330" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="L330">
+        <v>22</v>
+      </c>
+      <c r="M330">
+        <v>0</v>
+      </c>
+      <c r="N330">
+        <v>0.99</v>
+      </c>
+      <c r="O330">
+        <v>0.11505787037037037</v>
+      </c>
+      <c r="P330" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="331" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>199</v>
+      </c>
+      <c r="B331" t="s">
+        <v>19</v>
+      </c>
+      <c r="C331">
+        <v>1428099</v>
+      </c>
+      <c r="D331" t="s">
+        <v>84</v>
+      </c>
+      <c r="E331" t="s">
+        <v>16</v>
+      </c>
+      <c r="F331" t="s">
+        <v>17</v>
+      </c>
+      <c r="G331">
+        <v>29</v>
+      </c>
+      <c r="H331">
+        <v>1</v>
+      </c>
+      <c r="I331">
+        <v>29</v>
+      </c>
+      <c r="J331">
+        <v>0</v>
+      </c>
+      <c r="K331" s="2">
+        <v>1</v>
+      </c>
+      <c r="L331">
+        <v>29</v>
+      </c>
+      <c r="M331">
+        <v>0</v>
+      </c>
+      <c r="N331">
+        <v>0.95</v>
+      </c>
+      <c r="O331">
+        <v>0.14206018518518518</v>
+      </c>
+      <c r="P331" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="332" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>144</v>
+      </c>
+      <c r="B332" t="s">
+        <v>26</v>
+      </c>
+      <c r="C332">
+        <v>862502</v>
+      </c>
+      <c r="D332" t="s">
+        <v>31</v>
+      </c>
+      <c r="E332" t="s">
+        <v>16</v>
+      </c>
+      <c r="F332" t="s">
+        <v>17</v>
+      </c>
+      <c r="G332">
+        <v>62</v>
+      </c>
+      <c r="H332">
+        <v>1</v>
+      </c>
+      <c r="I332">
+        <v>62</v>
+      </c>
+      <c r="J332">
+        <v>0</v>
+      </c>
+      <c r="K332" s="2">
+        <v>1</v>
+      </c>
+      <c r="L332">
+        <v>62</v>
+      </c>
+      <c r="M332">
+        <v>0</v>
+      </c>
+      <c r="N332">
+        <v>0.96</v>
+      </c>
+      <c r="O332">
+        <v>0.29912037037037037</v>
+      </c>
+      <c r="P332" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="333" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>179</v>
+      </c>
+      <c r="B333" t="s">
+        <v>23</v>
+      </c>
+      <c r="C333">
+        <v>1404018</v>
+      </c>
+      <c r="D333" t="s">
+        <v>66</v>
+      </c>
+      <c r="E333" t="s">
+        <v>16</v>
+      </c>
+      <c r="F333" t="s">
+        <v>17</v>
+      </c>
+      <c r="G333">
+        <v>61</v>
+      </c>
+      <c r="H333">
+        <v>0.98</v>
+      </c>
+      <c r="I333">
+        <v>60</v>
+      </c>
+      <c r="J333">
+        <v>1</v>
+      </c>
+      <c r="K333" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="L333">
+        <v>60</v>
+      </c>
+      <c r="M333">
+        <v>0</v>
+      </c>
+      <c r="N333">
+        <v>0.93</v>
+      </c>
+      <c r="O333">
+        <v>0.2222685185185185</v>
+      </c>
+      <c r="P333" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="334" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>206</v>
+      </c>
+      <c r="B334" t="s">
+        <v>26</v>
+      </c>
+      <c r="C334">
+        <v>1440098</v>
+      </c>
+      <c r="D334" t="s">
+        <v>91</v>
+      </c>
+      <c r="E334" t="s">
+        <v>16</v>
+      </c>
+      <c r="F334" t="s">
+        <v>17</v>
+      </c>
+      <c r="G334">
+        <v>24</v>
+      </c>
+      <c r="H334">
+        <v>1</v>
+      </c>
+      <c r="I334">
+        <v>24</v>
+      </c>
+      <c r="J334">
+        <v>0</v>
+      </c>
+      <c r="K334" s="2">
+        <v>1</v>
+      </c>
+      <c r="L334">
+        <v>24</v>
+      </c>
+      <c r="M334">
+        <v>0</v>
+      </c>
+      <c r="N334">
+        <v>0.96</v>
+      </c>
+      <c r="O334">
+        <v>9.9907407407407403E-2</v>
+      </c>
+      <c r="P334" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="335" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>163</v>
+      </c>
+      <c r="B335" t="s">
+        <v>23</v>
+      </c>
+      <c r="C335">
+        <v>1145990</v>
+      </c>
+      <c r="D335" t="s">
+        <v>50</v>
+      </c>
+      <c r="E335" t="s">
+        <v>16</v>
+      </c>
+      <c r="F335" t="s">
+        <v>17</v>
+      </c>
+      <c r="G335">
+        <v>61</v>
+      </c>
+      <c r="H335">
+        <v>1</v>
+      </c>
+      <c r="I335">
+        <v>61</v>
+      </c>
+      <c r="J335">
+        <v>0</v>
+      </c>
+      <c r="K335" s="2">
+        <v>1</v>
+      </c>
+      <c r="L335">
+        <v>61</v>
+      </c>
+      <c r="M335">
+        <v>0</v>
+      </c>
+      <c r="N335">
+        <v>0.96</v>
+      </c>
+      <c r="O335">
+        <v>0.22238425925925928</v>
+      </c>
+      <c r="P335" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="336" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>214</v>
+      </c>
+      <c r="B336" t="s">
+        <v>23</v>
+      </c>
+      <c r="C336">
+        <v>1442138</v>
+      </c>
+      <c r="D336" t="s">
+        <v>99</v>
+      </c>
+      <c r="E336" t="s">
+        <v>16</v>
+      </c>
+      <c r="F336" t="s">
+        <v>17</v>
+      </c>
+      <c r="G336">
+        <v>23</v>
+      </c>
+      <c r="H336">
+        <v>0.96</v>
+      </c>
+      <c r="I336">
+        <v>22</v>
+      </c>
+      <c r="J336">
+        <v>1</v>
+      </c>
+      <c r="K336" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="L336">
+        <v>22</v>
+      </c>
+      <c r="M336">
+        <v>0</v>
+      </c>
+      <c r="N336">
+        <v>0.99</v>
+      </c>
+      <c r="O336">
+        <v>0.16459490740740743</v>
+      </c>
+      <c r="P336" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="337" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>194</v>
+      </c>
+      <c r="B337" t="s">
+        <v>23</v>
+      </c>
+      <c r="C337">
+        <v>1423385</v>
+      </c>
+      <c r="D337" t="s">
+        <v>80</v>
+      </c>
+      <c r="E337" t="s">
+        <v>16</v>
+      </c>
+      <c r="F337" t="s">
+        <v>17</v>
+      </c>
+      <c r="G337">
+        <v>36</v>
+      </c>
+      <c r="H337">
+        <v>1</v>
+      </c>
+      <c r="I337">
+        <v>36</v>
+      </c>
+      <c r="J337">
+        <v>0</v>
+      </c>
+      <c r="K337" s="2">
+        <v>1</v>
+      </c>
+      <c r="L337">
+        <v>36</v>
+      </c>
+      <c r="M337">
+        <v>0</v>
+      </c>
+      <c r="N337">
+        <v>0.99</v>
+      </c>
+      <c r="O337">
+        <v>0.14725694444444445</v>
+      </c>
+      <c r="P337" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="338" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>195</v>
+      </c>
+      <c r="B338" t="s">
+        <v>19</v>
+      </c>
+      <c r="C338">
+        <v>1424502</v>
+      </c>
+      <c r="D338" t="s">
+        <v>81</v>
+      </c>
+      <c r="E338" t="s">
+        <v>16</v>
+      </c>
+      <c r="F338" t="s">
+        <v>17</v>
+      </c>
+      <c r="G338">
+        <v>28</v>
+      </c>
+      <c r="H338">
+        <v>1</v>
+      </c>
+      <c r="I338">
+        <v>28</v>
+      </c>
+      <c r="J338">
+        <v>0</v>
+      </c>
+      <c r="K338" s="2">
+        <v>1</v>
+      </c>
+      <c r="L338">
+        <v>28</v>
+      </c>
+      <c r="M338">
+        <v>0</v>
+      </c>
+      <c r="N338">
+        <v>0.94</v>
+      </c>
+      <c r="O338">
+        <v>0.2559953703703704</v>
+      </c>
+      <c r="P338" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="339" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>137</v>
+      </c>
+      <c r="B339" t="s">
+        <v>23</v>
+      </c>
+      <c r="C339">
+        <v>845745</v>
+      </c>
+      <c r="D339" t="s">
+        <v>22</v>
+      </c>
+      <c r="E339" t="s">
+        <v>16</v>
+      </c>
+      <c r="F339" t="s">
+        <v>17</v>
+      </c>
+      <c r="G339">
+        <v>87</v>
+      </c>
+      <c r="H339">
+        <v>1</v>
+      </c>
+      <c r="I339">
+        <v>87</v>
+      </c>
+      <c r="J339">
+        <v>0</v>
+      </c>
+      <c r="K339" s="2">
+        <v>1</v>
+      </c>
+      <c r="L339">
+        <v>87</v>
+      </c>
+      <c r="M339">
+        <v>0</v>
+      </c>
+      <c r="N339">
+        <v>0.94</v>
+      </c>
+      <c r="O339">
+        <v>0.83035879629629628</v>
+      </c>
+      <c r="P339" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="340" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>269</v>
+      </c>
+      <c r="B340" t="s">
+        <v>23</v>
+      </c>
+      <c r="C340">
+        <v>847257</v>
+      </c>
+      <c r="D340" t="s">
+        <v>256</v>
+      </c>
+      <c r="E340" t="s">
+        <v>16</v>
+      </c>
+      <c r="F340" t="s">
+        <v>17</v>
+      </c>
+      <c r="G340">
+        <v>62</v>
+      </c>
+      <c r="H340">
+        <v>1</v>
+      </c>
+      <c r="I340">
+        <v>62</v>
+      </c>
+      <c r="J340">
+        <v>0</v>
+      </c>
+      <c r="K340" s="2">
+        <v>1</v>
+      </c>
+      <c r="L340">
+        <v>62</v>
+      </c>
+      <c r="M340">
+        <v>0</v>
+      </c>
+      <c r="N340">
+        <v>0.95</v>
+      </c>
+      <c r="O340">
+        <v>0.24847222222222221</v>
+      </c>
+      <c r="P340" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="341" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>270</v>
+      </c>
+      <c r="B341" t="s">
+        <v>26</v>
+      </c>
+      <c r="C341">
+        <v>1444974</v>
+      </c>
+      <c r="D341" t="s">
+        <v>257</v>
+      </c>
+      <c r="E341" t="s">
+        <v>16</v>
+      </c>
+      <c r="F341" t="s">
+        <v>17</v>
+      </c>
+      <c r="G341">
+        <v>22</v>
+      </c>
+      <c r="H341">
+        <v>1</v>
+      </c>
+      <c r="I341">
+        <v>22</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341" s="2">
+        <v>1</v>
+      </c>
+      <c r="L341">
+        <v>22</v>
+      </c>
+      <c r="M341">
+        <v>0</v>
+      </c>
+      <c r="N341">
+        <v>0.96</v>
+      </c>
+      <c r="O341">
+        <v>9.4224537037037037E-2</v>
+      </c>
+      <c r="P341" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="342" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>271</v>
+      </c>
+      <c r="B342" t="s">
+        <v>30</v>
+      </c>
+      <c r="C342">
+        <v>1444976</v>
+      </c>
+      <c r="D342" t="s">
+        <v>258</v>
+      </c>
+      <c r="E342" t="s">
+        <v>16</v>
+      </c>
+      <c r="F342" t="s">
+        <v>17</v>
+      </c>
+      <c r="G342">
+        <v>22</v>
+      </c>
+      <c r="H342">
+        <v>1</v>
+      </c>
+      <c r="I342">
+        <v>22</v>
+      </c>
+      <c r="J342">
+        <v>0</v>
+      </c>
+      <c r="K342" s="2">
+        <v>1</v>
+      </c>
+      <c r="L342">
+        <v>22</v>
+      </c>
+      <c r="M342">
+        <v>0</v>
+      </c>
+      <c r="N342">
+        <v>0.94</v>
+      </c>
+      <c r="O342">
+        <v>9.150462962962963E-2</v>
+      </c>
+      <c r="P342" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="343" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>272</v>
+      </c>
+      <c r="B343" t="s">
+        <v>30</v>
+      </c>
+      <c r="C343">
+        <v>1445535</v>
+      </c>
+      <c r="D343" t="s">
+        <v>259</v>
+      </c>
+      <c r="E343" t="s">
+        <v>16</v>
+      </c>
+      <c r="F343" t="s">
+        <v>17</v>
+      </c>
+      <c r="G343">
+        <v>18</v>
+      </c>
+      <c r="H343">
+        <v>1</v>
+      </c>
+      <c r="I343">
+        <v>18</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
+      </c>
+      <c r="K343" s="2">
+        <v>1</v>
+      </c>
+      <c r="L343">
+        <v>18</v>
+      </c>
+      <c r="M343">
+        <v>0</v>
+      </c>
+      <c r="N343">
+        <v>0.96</v>
+      </c>
+      <c r="O343">
+        <v>6.806712962962963E-2</v>
+      </c>
+      <c r="P343" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="344" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>273</v>
+      </c>
+      <c r="B344" t="s">
+        <v>30</v>
+      </c>
+      <c r="C344">
+        <v>1445493</v>
+      </c>
+      <c r="D344" t="s">
+        <v>260</v>
+      </c>
+      <c r="E344" t="s">
+        <v>16</v>
+      </c>
+      <c r="F344" t="s">
+        <v>17</v>
+      </c>
+      <c r="G344">
+        <v>22</v>
+      </c>
+      <c r="H344">
+        <v>0.95</v>
+      </c>
+      <c r="I344">
+        <v>21</v>
+      </c>
+      <c r="J344">
+        <v>1</v>
+      </c>
+      <c r="K344" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L344">
+        <v>21</v>
+      </c>
+      <c r="M344">
+        <v>0</v>
+      </c>
+      <c r="N344">
+        <v>0.98</v>
+      </c>
+      <c r="O344">
+        <v>9.5868055555555554E-2</v>
+      </c>
+      <c r="P344" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="345" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>274</v>
+      </c>
+      <c r="B345" t="s">
+        <v>26</v>
+      </c>
+      <c r="C345">
+        <v>1445513</v>
+      </c>
+      <c r="D345" t="s">
+        <v>261</v>
+      </c>
+      <c r="E345" t="s">
+        <v>16</v>
+      </c>
+      <c r="F345" t="s">
+        <v>17</v>
+      </c>
+      <c r="G345">
+        <v>22</v>
+      </c>
+      <c r="H345">
+        <v>0.95</v>
+      </c>
+      <c r="I345">
+        <v>21</v>
+      </c>
+      <c r="J345">
+        <v>1</v>
+      </c>
+      <c r="K345" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L345">
+        <v>21</v>
+      </c>
+      <c r="M345">
+        <v>0</v>
+      </c>
+      <c r="N345">
+        <v>0.99</v>
+      </c>
+      <c r="O345">
+        <v>9.6597222222222223E-2</v>
+      </c>
+      <c r="P345" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="346" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>275</v>
+      </c>
+      <c r="B346" t="s">
+        <v>30</v>
+      </c>
+      <c r="C346">
+        <v>1445516</v>
+      </c>
+      <c r="D346" t="s">
+        <v>262</v>
+      </c>
+      <c r="E346" t="s">
+        <v>16</v>
+      </c>
+      <c r="F346" t="s">
+        <v>17</v>
+      </c>
+      <c r="G346">
+        <v>22</v>
+      </c>
+      <c r="H346">
+        <v>0.95</v>
+      </c>
+      <c r="I346">
+        <v>21</v>
+      </c>
+      <c r="J346">
+        <v>1</v>
+      </c>
+      <c r="K346" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L346">
+        <v>21</v>
+      </c>
+      <c r="M346">
+        <v>0</v>
+      </c>
+      <c r="N346">
+        <v>0.99</v>
+      </c>
+      <c r="O346">
+        <v>0.10864583333333333</v>
+      </c>
+      <c r="P346" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="347" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>276</v>
+      </c>
+      <c r="B347" t="s">
+        <v>26</v>
+      </c>
+      <c r="C347">
+        <v>1445524</v>
+      </c>
+      <c r="D347" t="s">
+        <v>263</v>
+      </c>
+      <c r="E347" t="s">
+        <v>16</v>
+      </c>
+      <c r="F347" t="s">
+        <v>17</v>
+      </c>
+      <c r="G347">
+        <v>22</v>
+      </c>
+      <c r="H347">
+        <v>0.95</v>
+      </c>
+      <c r="I347">
+        <v>21</v>
+      </c>
+      <c r="J347">
+        <v>1</v>
+      </c>
+      <c r="K347" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L347">
+        <v>21</v>
+      </c>
+      <c r="M347">
+        <v>0</v>
+      </c>
+      <c r="N347">
+        <v>1</v>
+      </c>
+      <c r="O347">
+        <v>8.5185185185185183E-2</v>
+      </c>
+      <c r="P347" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="348" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>277</v>
+      </c>
+      <c r="B348" t="s">
+        <v>23</v>
+      </c>
+      <c r="C348">
+        <v>1445506</v>
+      </c>
+      <c r="D348" t="s">
+        <v>264</v>
+      </c>
+      <c r="E348" t="s">
+        <v>16</v>
+      </c>
+      <c r="F348" t="s">
+        <v>17</v>
+      </c>
+      <c r="G348">
+        <v>19</v>
+      </c>
+      <c r="H348">
+        <v>0.95</v>
+      </c>
+      <c r="I348">
+        <v>18</v>
+      </c>
+      <c r="J348">
+        <v>1</v>
+      </c>
+      <c r="K348" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L348">
+        <v>18</v>
+      </c>
+      <c r="M348">
+        <v>0</v>
+      </c>
+      <c r="N348">
+        <v>1</v>
+      </c>
+      <c r="O348">
+        <v>0.3122800925925926</v>
+      </c>
+      <c r="P348" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="349" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>278</v>
+      </c>
+      <c r="B349" t="s">
+        <v>23</v>
+      </c>
+      <c r="C349">
+        <v>1445512</v>
+      </c>
+      <c r="D349" t="s">
+        <v>265</v>
+      </c>
+      <c r="E349" t="s">
+        <v>16</v>
+      </c>
+      <c r="F349" t="s">
+        <v>17</v>
+      </c>
+      <c r="G349">
+        <v>19</v>
+      </c>
+      <c r="H349">
+        <v>0.95</v>
+      </c>
+      <c r="I349">
+        <v>18</v>
+      </c>
+      <c r="J349">
+        <v>1</v>
+      </c>
+      <c r="K349" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L349">
+        <v>18</v>
+      </c>
+      <c r="M349">
+        <v>0</v>
+      </c>
+      <c r="N349">
+        <v>1</v>
+      </c>
+      <c r="O349">
+        <v>0.10729166666666667</v>
+      </c>
+      <c r="P349" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="350" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>279</v>
+      </c>
+      <c r="B350" t="s">
+        <v>30</v>
+      </c>
+      <c r="C350">
+        <v>1445521</v>
+      </c>
+      <c r="D350" t="s">
+        <v>266</v>
+      </c>
+      <c r="E350" t="s">
+        <v>16</v>
+      </c>
+      <c r="F350" t="s">
+        <v>17</v>
+      </c>
+      <c r="G350">
+        <v>19</v>
+      </c>
+      <c r="H350">
+        <v>0.95</v>
+      </c>
+      <c r="I350">
+        <v>18</v>
+      </c>
+      <c r="J350">
+        <v>1</v>
+      </c>
+      <c r="K350" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="L350">
+        <v>18</v>
+      </c>
+      <c r="M350">
+        <v>0</v>
+      </c>
+      <c r="N350">
+        <v>0.99</v>
+      </c>
+      <c r="O350">
+        <v>9.6400462962962966E-2</v>
+      </c>
+      <c r="P350" s="1">
+        <v>46082</v>
       </c>
     </row>
   </sheetData>
